--- a/spreadsheet/hl.xlsx
+++ b/spreadsheet/hl.xlsx
@@ -1464,7 +1464,7 @@
           <t>Core UK Government Bond UCITS ETF</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>LU1407892592</t>
         </is>
@@ -1474,7 +1474,7 @@
           <t>https://www.hl.co.uk/shares/shares-search-results/a/amundi-core-uk-government-bond-ucits-et/company-information</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>This stock can be held in a Stocks and Shares ISA, Lifetime ISA, SIPP, Fund and Share Account</t>
         </is>
@@ -1486,7 +1486,7 @@
           <t>Core UK Government Inflation-Link UCITS ETF</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>LU1407893301</t>
         </is>
@@ -1496,7 +1496,7 @@
           <t>https://www.hl.co.uk/shares/shares-search-results/a/amundi-core-uk-government-inflation-link-uc/company-information</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>This stock can be held in a Stocks and Shares ISA, Lifetime ISA, SIPP, Fund and Share Account</t>
         </is>
@@ -1508,7 +1508,7 @@
           <t>Core US TIPS (DR) UCITS ETF</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>LU1452600270</t>
         </is>
@@ -1518,7 +1518,7 @@
           <t>https://www.hl.co.uk/shares/shares-search-results/a/amundi-core-us-tips-dr-ucits-etf/company-information</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>This stock can be held in a Stocks and Shares ISA, Lifetime ISA, SIPP, Fund and Share Account</t>
         </is>
@@ -1530,7 +1530,7 @@
           <t>Core US Tips DR UCITS ETF Monthly Hedged D-GBP</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>LU1452600601</t>
         </is>
@@ -1540,7 +1540,7 @@
           <t>https://www.hl.co.uk/shares/shares-search-results/a/amundi-core-us-tips-dr-ucits-etf-monthly-he/company-information</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>This stock can be held in a Stocks and Shares ISA, Lifetime ISA, SIPP, Fund and Share Account</t>
         </is>
@@ -1552,7 +1552,7 @@
           <t>DAX III UCITS ETF Accc</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>LU0252633754</t>
         </is>
@@ -1562,7 +1562,7 @@
           <t>https://www.hl.co.uk/shares/shares-search-results/a/amund-dax-iii-ucits-etf-acc/company-information</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>This stock can be held in a Stocks and Shares ISA, Lifetime ISA, SIPP, Fund and Share Account</t>
         </is>
@@ -5594,19 +5594,114 @@
       <c r="C11" s="11" t="n"/>
     </row>
     <row r="12" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="C12" s="12" t="n"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7IM Adventurous Fund (Class C)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GB0033957704</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/7/7im-adventurous-fund-class-c-income/key-features</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>You can buy or sell holdings in this fund through a Stocks and Shares ISA, Lifetime ISA, SIPP or Fund and Share Account</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="C13" s="12" t="n"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>7IM Adventurous Fund (Class C)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GB0033958009</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/7/7im-adventurous-fund-class-c-accumulation/key-features</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>You can buy or sell holdings in this fund through a Stocks and Shares ISA, Lifetime ISA, SIPP or Fund and Share Account</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="C14" s="12" t="n"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>7IM Balanced Fund (Class C)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GB0033959296</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/7/7im-balanced-fund-class-c-income/key-features</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>You can buy or sell holdings in this fund through a Stocks and Shares ISA, Lifetime ISA, SIPP or Fund and Share Account</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="C15" s="12" t="n"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>7IM Balanced Fund (Class C)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GB0033959742</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/7/7im-balanced-fund-class-c-accumulation/key-features</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>You can buy or sell holdings in this fund through a Stocks and Shares ISA, Lifetime ISA, SIPP or Fund and Share Account</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="C16" s="12" t="n"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>7IM Moderately Adventurous (Class C)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GB0033956391</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/7/7im-moderately-adventurous-class-c-income/key-features</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>You can buy or sell holdings in this fund through a Stocks and Shares ISA, Lifetime ISA, SIPP or Fund and Share Account</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="18" customFormat="1" customHeight="1" s="8">
       <c r="C17" s="12" t="n"/>
@@ -8564,6 +8659,13 @@
       <c r="C1001" s="12" t="n"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId5"/>
+  </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/spreadsheet/hl.xlsx
+++ b/spreadsheet/hl.xlsx
@@ -439,7 +439,7 @@
       </c>
     </row>
     <row r="2" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>3i Group Plc</t>
         </is>
@@ -451,7 +451,7 @@
       </c>
     </row>
     <row r="3" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>3i Infrastructure plc</t>
         </is>
@@ -463,7 +463,7 @@
       </c>
     </row>
     <row r="4" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Aberdeen Asia Focus Plc</t>
         </is>
@@ -475,7 +475,7 @@
       </c>
     </row>
     <row r="5" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Aberdeen Asian Income Fund Limited</t>
         </is>
@@ -487,7 +487,7 @@
       </c>
     </row>
     <row r="6" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Aberdeen Equity Income Trust Plc</t>
         </is>
@@ -499,7 +499,7 @@
       </c>
     </row>
     <row r="7" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Aberdeen New India Investmen Trust</t>
         </is>
@@ -511,7 +511,7 @@
       </c>
     </row>
     <row r="8" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Aberdeen UK Smaller Companies Growth Trust Plc</t>
         </is>
@@ -523,7 +523,7 @@
       </c>
     </row>
     <row r="9" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Aberforth Geared Value &amp; Income Trust Plc</t>
         </is>
@@ -535,7 +535,7 @@
       </c>
     </row>
     <row r="10" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Aberforth Smaller Companies Trust plc</t>
         </is>
@@ -547,7 +547,7 @@
       </c>
     </row>
     <row r="11" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Abrdn Diversified Income &amp; Growth Trust</t>
         </is>
@@ -559,7 +559,7 @@
       </c>
     </row>
     <row r="12" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Abrdn European Logistics Income Plc</t>
         </is>
@@ -571,7 +571,7 @@
       </c>
     </row>
     <row r="13" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Abrdn Property Income Trust Ltd</t>
         </is>
@@ -583,7 +583,7 @@
       </c>
     </row>
     <row r="14" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Achilles Investment Company Limited</t>
         </is>
@@ -595,7 +595,7 @@
       </c>
     </row>
     <row r="15" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>AEW UK REIT plc</t>
         </is>
@@ -607,7 +607,7 @@
       </c>
     </row>
     <row r="16" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Albion Crown VCT Plc</t>
         </is>
@@ -619,7 +619,7 @@
       </c>
     </row>
     <row r="17" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Albion Enterprise VCT plc</t>
         </is>
@@ -631,7 +631,7 @@
       </c>
     </row>
     <row r="18" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Albion Technology &amp; General VCT plc</t>
         </is>
@@ -643,7 +643,7 @@
       </c>
     </row>
     <row r="19" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Alliance Witan plc</t>
         </is>
@@ -655,7 +655,7 @@
       </c>
     </row>
     <row r="20" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Allianz Technology Trust plc</t>
         </is>
@@ -667,7 +667,7 @@
       </c>
     </row>
     <row r="21" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Alternative Income REIT</t>
         </is>
@@ -679,7 +679,7 @@
       </c>
     </row>
     <row r="22" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Amedeo Air Four Plus Ltd</t>
         </is>
@@ -691,7 +691,7 @@
       </c>
     </row>
     <row r="23" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Aquila Energy Efficiency Trust plc</t>
         </is>
@@ -703,7 +703,7 @@
       </c>
     </row>
     <row r="24" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Aquila European Renewables plc</t>
         </is>
@@ -715,7 +715,7 @@
       </c>
     </row>
     <row r="25" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Artemis UK Future Leaders plc</t>
         </is>
@@ -727,7 +727,7 @@
       </c>
     </row>
     <row r="26" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Ashoka India Equity Inv Trust Plc</t>
         </is>
@@ -739,7 +739,7 @@
       </c>
     </row>
     <row r="27" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Ashoka WhiteOak Emerging Markets Trust plc</t>
         </is>
@@ -751,7 +751,7 @@
       </c>
     </row>
     <row r="28" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>Athelney Trust</t>
         </is>
@@ -763,7 +763,7 @@
       </c>
     </row>
     <row r="29" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Augmentum Fintech plc</t>
         </is>
@@ -775,7 +775,7 @@
       </c>
     </row>
     <row r="30" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>Aurora UK Alpha Plc</t>
         </is>
@@ -787,7 +787,7 @@
       </c>
     </row>
     <row r="31" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>AVI Global Trust plc</t>
         </is>
@@ -799,7 +799,7 @@
       </c>
     </row>
     <row r="32" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>AVI Japan Opportunity Trust Plc</t>
         </is>
@@ -811,7 +811,7 @@
       </c>
     </row>
     <row r="33" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>Baillie Gifford China Growth Trust plc</t>
         </is>
@@ -823,7 +823,7 @@
       </c>
     </row>
     <row r="34" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>Baillie Gifford European Growth Trust Plc</t>
         </is>
@@ -835,7 +835,7 @@
       </c>
     </row>
     <row r="35" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>Baillie Gifford Japan Trust plc</t>
         </is>
@@ -847,7 +847,7 @@
       </c>
     </row>
     <row r="36" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>Baillie Gifford Shin Nippon plc</t>
         </is>
@@ -859,7 +859,7 @@
       </c>
     </row>
     <row r="37" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Baillie Gifford UK Growth Trust plc</t>
         </is>
@@ -871,7 +871,7 @@
       </c>
     </row>
     <row r="38" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Baillie Gifford US Growth Trust plc</t>
         </is>
@@ -883,7 +883,7 @@
       </c>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>Baker Steel Resources Trust Ltd</t>
         </is>
@@ -895,7 +895,7 @@
       </c>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>Bankers Investment Trust plc</t>
         </is>
@@ -907,7 +907,7 @@
       </c>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>Barings Emerging EMEA Opportunities</t>
         </is>
@@ -919,7 +919,7 @@
       </c>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>Baronsmead Second Venture Trust plc</t>
         </is>
@@ -931,7 +931,7 @@
       </c>
     </row>
     <row r="43" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>Baronsmead Venture Trust plc</t>
         </is>
@@ -943,7 +943,7 @@
       </c>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>BH Macro Ltd</t>
         </is>
@@ -955,7 +955,7 @@
       </c>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>BH Macro Ltd</t>
         </is>
@@ -967,7 +967,7 @@
       </c>
     </row>
     <row r="46" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>BioPharma Credit plc</t>
         </is>
@@ -979,7 +979,7 @@
       </c>
     </row>
     <row r="47" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>BioPharma Credit Plc</t>
         </is>
@@ -991,7 +991,7 @@
       </c>
     </row>
     <row r="48" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>Biotech Growth Trust plc (The)</t>
         </is>
@@ -1003,7 +1003,7 @@
       </c>
     </row>
     <row r="49" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>Blackfinch plc</t>
         </is>
@@ -1015,7 +1015,7 @@
       </c>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>BlackRock American Income Trust Plc</t>
         </is>
@@ -1027,7 +1027,7 @@
       </c>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>BlackRock Energy And Resources Income Trust plc</t>
         </is>
@@ -1039,7 +1039,7 @@
       </c>
     </row>
     <row r="52" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>BlackRock Frontiers Investment Trust plc</t>
         </is>
@@ -1051,7 +1051,7 @@
       </c>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>BlackRock Greater Europe Investment Trust plc</t>
         </is>
@@ -1063,7 +1063,7 @@
       </c>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>BlackRock Income &amp; Growth Investment Trust plc</t>
         </is>
@@ -1075,7 +1075,7 @@
       </c>
     </row>
     <row r="55" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>BlackRock Latin American Investment Trust plc</t>
         </is>
@@ -1087,7 +1087,7 @@
       </c>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>BlackRock Smaller Companies Trust plc</t>
         </is>
@@ -1099,7 +1099,7 @@
       </c>
     </row>
     <row r="57" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>BlackRock World Mining Trust plc</t>
         </is>
@@ -1111,7 +1111,7 @@
       </c>
     </row>
     <row r="58" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>Blue Star Capital plc</t>
         </is>
@@ -1123,7 +1123,7 @@
       </c>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>Bluefield Solar Income Fund Limited</t>
         </is>
@@ -1135,7 +1135,7 @@
       </c>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>British &amp; American Investment Trust plc</t>
         </is>
@@ -1147,7 +1147,7 @@
       </c>
     </row>
     <row r="61" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>British Smaller Companies VCT plc</t>
         </is>
@@ -1159,7 +1159,7 @@
       </c>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>British Smaller Companies VCT2 plc</t>
         </is>
@@ -1171,7 +1171,7 @@
       </c>
     </row>
     <row r="63" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>Brown Advisory US Smaller Companies</t>
         </is>
@@ -1183,7 +1183,7 @@
       </c>
     </row>
     <row r="64" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>Brunner Investment Trust plc</t>
         </is>
@@ -1195,7 +1195,7 @@
       </c>
     </row>
     <row r="65" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>Calculus VCT plc</t>
         </is>
@@ -1207,7 +1207,7 @@
       </c>
     </row>
     <row r="66" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>Caledonia Investments plc</t>
         </is>
@@ -1219,7 +1219,7 @@
       </c>
     </row>
     <row r="67" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>Canadian General Investments Ltd</t>
         </is>
@@ -1231,7 +1231,7 @@
       </c>
     </row>
     <row r="68" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="8" t="inlineStr">
         <is>
           <t>Capital for Colleagues plc</t>
         </is>
@@ -1243,7 +1243,7 @@
       </c>
     </row>
     <row r="69" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>Capital Gearing Trust plc</t>
         </is>
@@ -1255,7 +1255,7 @@
       </c>
     </row>
     <row r="70" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="8" t="inlineStr">
         <is>
           <t>Castelnau Group Ltd</t>
         </is>
@@ -1267,7 +1267,7 @@
       </c>
     </row>
     <row r="71" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="8" t="inlineStr">
         <is>
           <t>CC Japan Income &amp; Growth Trust plc</t>
         </is>
@@ -1279,7 +1279,7 @@
       </c>
     </row>
     <row r="72" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>Ceiba Investments Ltd</t>
         </is>
@@ -1291,7 +1291,7 @@
       </c>
     </row>
     <row r="73" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="8" t="inlineStr">
         <is>
           <t>Chelverton UK Dividend Trust plc</t>
         </is>
@@ -1303,7 +1303,7 @@
       </c>
     </row>
     <row r="74" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="8" t="inlineStr">
         <is>
           <t>Chenavari Toro Income Fund Ltd</t>
         </is>
@@ -1315,7 +1315,7 @@
       </c>
     </row>
     <row r="75" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>Chrysalis Investments Limited</t>
         </is>
@@ -1327,7 +1327,7 @@
       </c>
     </row>
     <row r="76" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="8" t="inlineStr">
         <is>
           <t>City Of London Investment Trust</t>
         </is>
@@ -1339,7 +1339,7 @@
       </c>
     </row>
     <row r="77" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="8" t="inlineStr">
         <is>
           <t>Cordiant Digital Infrastructure Limited</t>
         </is>
@@ -1351,7 +1351,7 @@
       </c>
     </row>
     <row r="78" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="8" t="inlineStr">
         <is>
           <t>CQS Natural Resources Growth and Income plc</t>
         </is>
@@ -1363,7 +1363,7 @@
       </c>
     </row>
     <row r="79" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="8" t="inlineStr">
         <is>
           <t>CQS New City High Yield Fund Ltd</t>
         </is>
@@ -1375,7 +1375,7 @@
       </c>
     </row>
     <row r="80" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="8" t="inlineStr">
         <is>
           <t>Crystal Amber Fund Ltd</t>
         </is>
@@ -1387,7 +1387,7 @@
       </c>
     </row>
     <row r="81" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="8" t="inlineStr">
         <is>
           <t>CT Global Managed Portfolio Trust plc</t>
         </is>
@@ -1399,7 +1399,7 @@
       </c>
     </row>
     <row r="82" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>CT Global Managed Portfolio Trust Plc</t>
         </is>
@@ -1411,7 +1411,7 @@
       </c>
     </row>
     <row r="83" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="8" t="inlineStr">
         <is>
           <t>CT Healthcare Trust plc</t>
         </is>
@@ -1423,7 +1423,7 @@
       </c>
     </row>
     <row r="84" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="8" t="inlineStr">
         <is>
           <t>CT Private Equity Trust Plc</t>
         </is>
@@ -1435,7 +1435,7 @@
       </c>
     </row>
     <row r="85" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="8" t="inlineStr">
         <is>
           <t>CT UK Capital &amp; Income Inv Trust plc</t>
         </is>
@@ -1447,7 +1447,7 @@
       </c>
     </row>
     <row r="86" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="8" t="inlineStr">
         <is>
           <t>CT UK High Income Trust plc</t>
         </is>
@@ -1459,7 +1459,7 @@
       </c>
     </row>
     <row r="87" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="8" t="inlineStr">
         <is>
           <t>CT UK High Income Trust plc</t>
         </is>
@@ -1471,7 +1471,7 @@
       </c>
     </row>
     <row r="88" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="8" t="inlineStr">
         <is>
           <t>Custodian Property Income REIT plc</t>
         </is>
@@ -1483,7 +1483,7 @@
       </c>
     </row>
     <row r="89" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t>CVC Income &amp; Growth Limited</t>
         </is>
@@ -1495,7 +1495,7 @@
       </c>
     </row>
     <row r="90" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="8" t="inlineStr">
         <is>
           <t>Develop North plc</t>
         </is>
@@ -1507,7 +1507,7 @@
       </c>
     </row>
     <row r="91" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="8" t="inlineStr">
         <is>
           <t>Digital 9 Infrastructure plc</t>
         </is>
@@ -1519,7 +1519,7 @@
       </c>
     </row>
     <row r="92" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="8" t="inlineStr">
         <is>
           <t>Diverse Income Trust plc (The)</t>
         </is>
@@ -1531,7 +1531,7 @@
       </c>
     </row>
     <row r="93" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="8" t="inlineStr">
         <is>
           <t>DP Aircraft I Limited</t>
         </is>
@@ -1543,7 +1543,7 @@
       </c>
     </row>
     <row r="94" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="8" t="inlineStr">
         <is>
           <t>Dunedin Income Growth Investment Trust plc</t>
         </is>
@@ -1555,7 +1555,7 @@
       </c>
     </row>
     <row r="95" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="8" t="inlineStr">
         <is>
           <t>Ecofin Global Utilities &amp; Infrastructure Trust plc</t>
         </is>
@@ -1567,7 +1567,7 @@
       </c>
     </row>
     <row r="96" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t>Ecofin US Renewables Infrastructure Trust</t>
         </is>
@@ -1579,7 +1579,7 @@
       </c>
     </row>
     <row r="97" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="8" t="inlineStr">
         <is>
           <t>Edinburgh Investment Trust plc</t>
         </is>
@@ -1591,7 +1591,7 @@
       </c>
     </row>
     <row r="98" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="8" t="inlineStr">
         <is>
           <t>Edinburgh Worldwide Investment Trust</t>
         </is>
@@ -1603,7 +1603,7 @@
       </c>
     </row>
     <row r="99" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="8" t="inlineStr">
         <is>
           <t>EJF Investments Ltd</t>
         </is>
@@ -1615,7 +1615,7 @@
       </c>
     </row>
     <row r="100" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="8" t="inlineStr">
         <is>
           <t>EPE Special Opportunities Limited</t>
         </is>
@@ -1627,7 +1627,7 @@
       </c>
     </row>
     <row r="101" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="8" t="inlineStr">
         <is>
           <t>European Opportunities Trust plc</t>
         </is>
@@ -1639,7 +1639,7 @@
       </c>
     </row>
     <row r="102" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="8" t="inlineStr">
         <is>
           <t>F&amp;C Investment Trust plc</t>
         </is>
@@ -1651,7 +1651,7 @@
       </c>
     </row>
     <row r="103" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="8" t="inlineStr">
         <is>
           <t>Fair Oaks Income Limited</t>
         </is>
@@ -1663,7 +1663,7 @@
       </c>
     </row>
     <row r="104" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="8" t="inlineStr">
         <is>
           <t>Fair Oaks Income Ltd</t>
         </is>
@@ -1675,7 +1675,7 @@
       </c>
     </row>
     <row r="105" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="8" t="inlineStr">
         <is>
           <t>Fidelity Asian Values plc</t>
         </is>
@@ -1687,7 +1687,7 @@
       </c>
     </row>
     <row r="106" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="8" t="inlineStr">
         <is>
           <t>Fidelity China Special Situations PLC</t>
         </is>
@@ -1699,7 +1699,7 @@
       </c>
     </row>
     <row r="107" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="8" t="inlineStr">
         <is>
           <t>Fidelity Emerging Markets Limited</t>
         </is>
@@ -1711,7 +1711,7 @@
       </c>
     </row>
     <row r="108" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="8" t="inlineStr">
         <is>
           <t>Fidelity European Trust plc</t>
         </is>
@@ -1723,7 +1723,7 @@
       </c>
     </row>
     <row r="109" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="8" t="inlineStr">
         <is>
           <t>Fidelity Special Values plc</t>
         </is>
@@ -1735,7 +1735,7 @@
       </c>
     </row>
     <row r="110" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="8" t="inlineStr">
         <is>
           <t>Finsbury Growth &amp; Income Trust plc</t>
         </is>
@@ -1747,7 +1747,7 @@
       </c>
     </row>
     <row r="111" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="8" t="inlineStr">
         <is>
           <t>Foresight Enterprise VCT</t>
         </is>
@@ -1759,7 +1759,7 @@
       </c>
     </row>
     <row r="112" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="8" t="inlineStr">
         <is>
           <t>Foresight Environmental Infrastructure Ltd</t>
         </is>
@@ -1771,7 +1771,7 @@
       </c>
     </row>
     <row r="113" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="8" t="inlineStr">
         <is>
           <t>Foresight Solar Fund Ltd</t>
         </is>
@@ -1783,7 +1783,7 @@
       </c>
     </row>
     <row r="114" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="8" t="inlineStr">
         <is>
           <t>Foresight Technology VCT plc</t>
         </is>
@@ -1795,7 +1795,7 @@
       </c>
     </row>
     <row r="115" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="8" t="inlineStr">
         <is>
           <t>Foresight VCT plc</t>
         </is>
@@ -1807,7 +1807,7 @@
       </c>
     </row>
     <row r="116" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="8" t="inlineStr">
         <is>
           <t>Foresight Ventures VCT Plc</t>
         </is>
@@ -1819,7 +1819,7 @@
       </c>
     </row>
     <row r="117" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="8" t="inlineStr">
         <is>
           <t>Fuel Ventures VCT plc</t>
         </is>
@@ -1831,7 +1831,7 @@
       </c>
     </row>
     <row r="118" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="8" t="inlineStr">
         <is>
           <t>Gabelli Merchant Partners Plc</t>
         </is>
@@ -1843,7 +1843,7 @@
       </c>
     </row>
     <row r="119" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="8" t="inlineStr">
         <is>
           <t>GCP Asset Backed Income Fund Limited</t>
         </is>
@@ -1855,7 +1855,7 @@
       </c>
     </row>
     <row r="120" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="8" t="inlineStr">
         <is>
           <t>GCP Infrastructure Investments Ltd</t>
         </is>
@@ -1867,7 +1867,7 @@
       </c>
     </row>
     <row r="121" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="8" t="inlineStr">
         <is>
           <t>Geiger Counter Ltd</t>
         </is>
@@ -1879,7 +1879,7 @@
       </c>
     </row>
     <row r="122" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="8" t="inlineStr">
         <is>
           <t>Global Opportunities Trust plc</t>
         </is>
@@ -1891,7 +1891,7 @@
       </c>
     </row>
     <row r="123" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="8" t="inlineStr">
         <is>
           <t>Golden Prospect Precious Metals Ltd</t>
         </is>
@@ -1903,7 +1903,7 @@
       </c>
     </row>
     <row r="124" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="8" t="inlineStr">
         <is>
           <t>Gore Street Energy Storage Fund plc</t>
         </is>
@@ -1915,7 +1915,7 @@
       </c>
     </row>
     <row r="125" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="8" t="inlineStr">
         <is>
           <t>Greencoat Renewables plc</t>
         </is>
@@ -1927,7 +1927,7 @@
       </c>
     </row>
     <row r="126" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="8" t="inlineStr">
         <is>
           <t>Greencoat UK Wind plc</t>
         </is>
@@ -1939,7 +1939,7 @@
       </c>
     </row>
     <row r="127" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="8" t="inlineStr">
         <is>
           <t>Gresham House Energy Storage Fund Plc</t>
         </is>
@@ -1951,7 +1951,7 @@
       </c>
     </row>
     <row r="128" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="8" t="inlineStr">
         <is>
           <t>Gresham House Income &amp; Growth 2 VCT Plc</t>
         </is>
@@ -1963,7 +1963,7 @@
       </c>
     </row>
     <row r="129" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="8" t="inlineStr">
         <is>
           <t>Gresham House Income &amp; Growth VCT Plc</t>
         </is>
@@ -1975,7 +1975,7 @@
       </c>
     </row>
     <row r="130" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="8" t="inlineStr">
         <is>
           <t>Gresham House Renewable Energy VCT 1 Plc</t>
         </is>
@@ -1987,7 +1987,7 @@
       </c>
     </row>
     <row r="131" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="8" t="inlineStr">
         <is>
           <t>Gresham House Renewable Energy VCT 2 Plc</t>
         </is>
@@ -1999,7 +1999,7 @@
       </c>
     </row>
     <row r="132" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="8" t="inlineStr">
         <is>
           <t>Gresham House Renewable Energy VCT2 plc</t>
         </is>
@@ -2011,7 +2011,7 @@
       </c>
     </row>
     <row r="133" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="8" t="inlineStr">
         <is>
           <t>Gresham House Renewable VCT 1 plc</t>
         </is>
@@ -2023,7 +2023,7 @@
       </c>
     </row>
     <row r="134" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A134" t="inlineStr">
+      <c r="A134" s="8" t="inlineStr">
         <is>
           <t>Ground Rents Income Fund plc</t>
         </is>
@@ -2035,7 +2035,7 @@
       </c>
     </row>
     <row r="135" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="8" t="inlineStr">
         <is>
           <t>Guinness VCT plc</t>
         </is>
@@ -2047,7 +2047,7 @@
       </c>
     </row>
     <row r="136" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A136" t="inlineStr">
+      <c r="A136" s="8" t="inlineStr">
         <is>
           <t>Hansa Investment Company Limited</t>
         </is>
@@ -2059,7 +2059,7 @@
       </c>
     </row>
     <row r="137" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="8" t="inlineStr">
         <is>
           <t>Hansa Investment Company Limited</t>
         </is>
@@ -2071,7 +2071,7 @@
       </c>
     </row>
     <row r="138" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="8" t="inlineStr">
         <is>
           <t>Harbourvest Global Private Equity</t>
         </is>
@@ -2083,7 +2083,7 @@
       </c>
     </row>
     <row r="139" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="8" t="inlineStr">
         <is>
           <t>Hargreave Hale AIM VCT Plc</t>
         </is>
@@ -2095,7 +2095,7 @@
       </c>
     </row>
     <row r="140" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A140" t="inlineStr">
+      <c r="A140" s="8" t="inlineStr">
         <is>
           <t>Henderson Far East Income Ltd</t>
         </is>
@@ -2107,7 +2107,7 @@
       </c>
     </row>
     <row r="141" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A141" t="inlineStr">
+      <c r="A141" s="8" t="inlineStr">
         <is>
           <t>Henderson High Income Trust plc</t>
         </is>
@@ -2119,7 +2119,7 @@
       </c>
     </row>
     <row r="142" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A142" t="inlineStr">
+      <c r="A142" s="8" t="inlineStr">
         <is>
           <t>Henderson Smaller Cos Investment Trust plc</t>
         </is>
@@ -2131,7 +2131,7 @@
       </c>
     </row>
     <row r="143" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A143" t="inlineStr">
+      <c r="A143" s="8" t="inlineStr">
         <is>
           <t>Herald Investment Trust plc</t>
         </is>
@@ -2143,7 +2143,7 @@
       </c>
     </row>
     <row r="144" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A144" t="inlineStr">
+      <c r="A144" s="8" t="inlineStr">
         <is>
           <t>HG Capital Trust plc</t>
         </is>
@@ -2155,7 +2155,7 @@
       </c>
     </row>
     <row r="145" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A145" t="inlineStr">
+      <c r="A145" s="8" t="inlineStr">
         <is>
           <t>HICL Infrastructure plc</t>
         </is>
@@ -2167,7 +2167,7 @@
       </c>
     </row>
     <row r="146" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A146" t="inlineStr">
+      <c r="A146" s="8" t="inlineStr">
         <is>
           <t>Home REIT plc</t>
         </is>
@@ -2179,7 +2179,7 @@
       </c>
     </row>
     <row r="147" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A147" t="inlineStr">
+      <c r="A147" s="8" t="inlineStr">
         <is>
           <t>Hydrogen Capital Growth Plc</t>
         </is>
@@ -2191,7 +2191,7 @@
       </c>
     </row>
     <row r="148" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A148" t="inlineStr">
+      <c r="A148" s="8" t="inlineStr">
         <is>
           <t>ICG Enterprise Trust plc</t>
         </is>
@@ -2203,7 +2203,7 @@
       </c>
     </row>
     <row r="149" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A149" t="inlineStr">
+      <c r="A149" s="8" t="inlineStr">
         <is>
           <t>ICG-Longbow Senior Secured UK Property Debt Invest</t>
         </is>
@@ -2215,7 +2215,7 @@
       </c>
     </row>
     <row r="150" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A150" t="inlineStr">
+      <c r="A150" s="8" t="inlineStr">
         <is>
           <t>Impax Environmental Markets plc</t>
         </is>
@@ -2227,7 +2227,7 @@
       </c>
     </row>
     <row r="151" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A151" t="inlineStr">
+      <c r="A151" s="8" t="inlineStr">
         <is>
           <t>India Capital Growth Fund Ltd</t>
         </is>
@@ -2239,7 +2239,7 @@
       </c>
     </row>
     <row r="152" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A152" t="inlineStr">
+      <c r="A152" s="8" t="inlineStr">
         <is>
           <t>International Biotechnology Trust plc</t>
         </is>
@@ -2251,7 +2251,7 @@
       </c>
     </row>
     <row r="153" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A153" t="inlineStr">
+      <c r="A153" s="8" t="inlineStr">
         <is>
           <t>International Public Partnerships Limited</t>
         </is>
@@ -2263,7 +2263,7 @@
       </c>
     </row>
     <row r="154" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A154" t="inlineStr">
+      <c r="A154" s="8" t="inlineStr">
         <is>
           <t>Intuitive Investments Group plc</t>
         </is>
@@ -2275,7 +2275,7 @@
       </c>
     </row>
     <row r="155" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A155" t="inlineStr">
+      <c r="A155" s="8" t="inlineStr">
         <is>
           <t>Invesco Asia Dragon Trust Plc</t>
         </is>
@@ -2287,7 +2287,7 @@
       </c>
     </row>
     <row r="156" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A156" t="inlineStr">
+      <c r="A156" s="8" t="inlineStr">
         <is>
           <t>Invesco Bond Income Plus Limited</t>
         </is>
@@ -2299,7 +2299,7 @@
       </c>
     </row>
     <row r="157" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A157" t="inlineStr">
+      <c r="A157" s="8" t="inlineStr">
         <is>
           <t>Invesco Global Equity Income Trust plc</t>
         </is>
@@ -2311,7 +2311,7 @@
       </c>
     </row>
     <row r="158" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A158" t="inlineStr">
+      <c r="A158" s="8" t="inlineStr">
         <is>
           <t>Investment Co plc</t>
         </is>
@@ -2323,7 +2323,7 @@
       </c>
     </row>
     <row r="159" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A159" t="inlineStr">
+      <c r="A159" s="8" t="inlineStr">
         <is>
           <t>JPMorgan American Investment Trust plc</t>
         </is>
@@ -2335,7 +2335,7 @@
       </c>
     </row>
     <row r="160" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A160" t="inlineStr">
+      <c r="A160" s="8" t="inlineStr">
         <is>
           <t>JPMorgan Asia Growth and Income Plc</t>
         </is>
@@ -2347,7 +2347,7 @@
       </c>
     </row>
     <row r="161" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A161" t="inlineStr">
+      <c r="A161" s="8" t="inlineStr">
         <is>
           <t>JPMorgan China Growth &amp; Income Plc</t>
         </is>
@@ -2359,7 +2359,7 @@
       </c>
     </row>
     <row r="162" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A162" t="inlineStr">
+      <c r="A162" s="8" t="inlineStr">
         <is>
           <t>JPMorgan Claverhouse Investment Trust plc</t>
         </is>
@@ -2371,7 +2371,7 @@
       </c>
     </row>
     <row r="163" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A163" t="inlineStr">
+      <c r="A163" s="8" t="inlineStr">
         <is>
           <t>JPMorgan Emerging Europe, Middle East &amp; Africa Sec</t>
         </is>
@@ -2383,7 +2383,7 @@
       </c>
     </row>
     <row r="164" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A164" t="inlineStr">
+      <c r="A164" s="8" t="inlineStr">
         <is>
           <t>JPMorgan Emerging Markets Dividend Income Plc</t>
         </is>
@@ -2395,7 +2395,7 @@
       </c>
     </row>
     <row r="165" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A165" t="inlineStr">
+      <c r="A165" s="8" t="inlineStr">
         <is>
           <t>JPMorgan Emerging Markets Growth &amp; Income Plc</t>
         </is>
@@ -2407,7 +2407,7 @@
       </c>
     </row>
     <row r="166" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A166" t="inlineStr">
+      <c r="A166" s="8" t="inlineStr">
         <is>
           <t>JPMorgan European Discovery Trust plc</t>
         </is>
@@ -2419,7 +2419,7 @@
       </c>
     </row>
     <row r="167" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A167" t="inlineStr">
+      <c r="A167" s="8" t="inlineStr">
         <is>
           <t>JPMorgan European Growth &amp; Income plc</t>
         </is>
@@ -2431,7 +2431,7 @@
       </c>
     </row>
     <row r="168" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A168" t="inlineStr">
+      <c r="A168" s="8" t="inlineStr">
         <is>
           <t>JPMorgan Global Core Real Assets Ltd</t>
         </is>
@@ -2443,7 +2443,7 @@
       </c>
     </row>
     <row r="169" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A169" t="inlineStr">
+      <c r="A169" s="8" t="inlineStr">
         <is>
           <t>JPMorgan Global Growth &amp; Income plc</t>
         </is>
@@ -2455,7 +2455,7 @@
       </c>
     </row>
     <row r="170" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A170" t="inlineStr">
+      <c r="A170" s="8" t="inlineStr">
         <is>
           <t>JPMorgan India Growth &amp; Income plc</t>
         </is>
@@ -2467,7 +2467,7 @@
       </c>
     </row>
     <row r="171" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A171" t="inlineStr">
+      <c r="A171" s="8" t="inlineStr">
         <is>
           <t>JPMorgan Japanese Investment Trust plc</t>
         </is>
@@ -2479,7 +2479,7 @@
       </c>
     </row>
     <row r="172" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A172" t="inlineStr">
+      <c r="A172" s="8" t="inlineStr">
         <is>
           <t>JPMorgan UK Small Cap Growth &amp; Income plc</t>
         </is>
@@ -2491,7 +2491,7 @@
       </c>
     </row>
     <row r="173" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A173" t="inlineStr">
+      <c r="A173" s="8" t="inlineStr">
         <is>
           <t>JPMorgan US Smaller Companies Investment Trust plc</t>
         </is>
@@ -2503,7 +2503,7 @@
       </c>
     </row>
     <row r="174" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A174" t="inlineStr">
+      <c r="A174" s="8" t="inlineStr">
         <is>
           <t>JZ Capital Partners Ltd</t>
         </is>
@@ -2515,7 +2515,7 @@
       </c>
     </row>
     <row r="175" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A175" t="inlineStr">
+      <c r="A175" s="8" t="inlineStr">
         <is>
           <t>Law Debenture Corporation plc</t>
         </is>
@@ -2527,7 +2527,7 @@
       </c>
     </row>
     <row r="176" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A176" t="inlineStr">
+      <c r="A176" s="8" t="inlineStr">
         <is>
           <t>Life Science REIT</t>
         </is>
@@ -2539,7 +2539,7 @@
       </c>
     </row>
     <row r="177" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A177" t="inlineStr">
+      <c r="A177" s="8" t="inlineStr">
         <is>
           <t>Life Settlement Assets plc</t>
         </is>
@@ -2551,7 +2551,7 @@
       </c>
     </row>
     <row r="178" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A178" t="inlineStr">
+      <c r="A178" s="8" t="inlineStr">
         <is>
           <t>Lindsell Train Investment Trust plc</t>
         </is>
@@ -2563,7 +2563,7 @@
       </c>
     </row>
     <row r="179" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A179" t="inlineStr">
+      <c r="A179" s="8" t="inlineStr">
         <is>
           <t>Literacy Capital plc</t>
         </is>
@@ -2575,7 +2575,7 @@
       </c>
     </row>
     <row r="180" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A180" t="inlineStr">
+      <c r="A180" s="8" t="inlineStr">
         <is>
           <t>LMS Capital plc</t>
         </is>
@@ -2587,7 +2587,7 @@
       </c>
     </row>
     <row r="181" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A181" t="inlineStr">
+      <c r="A181" s="8" t="inlineStr">
         <is>
           <t>Lowland Investment Company plc</t>
         </is>
@@ -2599,7 +2599,7 @@
       </c>
     </row>
     <row r="182" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A182" t="inlineStr">
+      <c r="A182" s="8" t="inlineStr">
         <is>
           <t>M&amp;G Credit Income Investment Trust plc</t>
         </is>
@@ -2611,7 +2611,7 @@
       </c>
     </row>
     <row r="183" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A183" t="inlineStr">
+      <c r="A183" s="8" t="inlineStr">
         <is>
           <t>Macau Property Opportunities Fund</t>
         </is>
@@ -2623,7 +2623,7 @@
       </c>
     </row>
     <row r="184" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A184" t="inlineStr">
+      <c r="A184" s="8" t="inlineStr">
         <is>
           <t>Majedie Investments plc</t>
         </is>
@@ -2635,7 +2635,7 @@
       </c>
     </row>
     <row r="185" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A185" t="inlineStr">
+      <c r="A185" s="8" t="inlineStr">
         <is>
           <t>Manchester &amp; London Inv Tst plc</t>
         </is>
@@ -2647,7 +2647,7 @@
       </c>
     </row>
     <row r="186" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A186" t="inlineStr">
+      <c r="A186" s="8" t="inlineStr">
         <is>
           <t>Marwyn Value Investors Ltd</t>
         </is>
@@ -2659,7 +2659,7 @@
       </c>
     </row>
     <row r="187" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A187" t="inlineStr">
+      <c r="A187" s="8" t="inlineStr">
         <is>
           <t>Maven Income &amp; Growth VCT 4 plc</t>
         </is>
@@ -2671,7 +2671,7 @@
       </c>
     </row>
     <row r="188" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A188" t="inlineStr">
+      <c r="A188" s="8" t="inlineStr">
         <is>
           <t>Maven Income &amp; Growth VCT 5 plc</t>
         </is>
@@ -2683,7 +2683,7 @@
       </c>
     </row>
     <row r="189" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A189" t="inlineStr">
+      <c r="A189" s="8" t="inlineStr">
         <is>
           <t>Maven Income &amp; Growth VCT plc</t>
         </is>
@@ -2695,7 +2695,7 @@
       </c>
     </row>
     <row r="190" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A190" t="inlineStr">
+      <c r="A190" s="8" t="inlineStr">
         <is>
           <t>Maven Income and Growth VCT 3 plc</t>
         </is>
@@ -2707,7 +2707,7 @@
       </c>
     </row>
     <row r="191" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A191" t="inlineStr">
+      <c r="A191" s="8" t="inlineStr">
         <is>
           <t>Maven Renovar VCT Plc</t>
         </is>
@@ -2719,7 +2719,7 @@
       </c>
     </row>
     <row r="192" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A192" t="inlineStr">
+      <c r="A192" s="8" t="inlineStr">
         <is>
           <t>Mercantile Investment Trust Plc</t>
         </is>
@@ -2731,7 +2731,7 @@
       </c>
     </row>
     <row r="193" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A193" t="inlineStr">
+      <c r="A193" s="8" t="inlineStr">
         <is>
           <t>Merchants Trust plc</t>
         </is>
@@ -2743,7 +2743,7 @@
       </c>
     </row>
     <row r="194" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A194" t="inlineStr">
+      <c r="A194" s="8" t="inlineStr">
         <is>
           <t>Mid Wynd International Investment Trust Plc</t>
         </is>
@@ -2755,7 +2755,7 @@
       </c>
     </row>
     <row r="195" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A195" t="inlineStr">
+      <c r="A195" s="8" t="inlineStr">
         <is>
           <t>Migo Opportunities Trust Plc</t>
         </is>
@@ -2767,7 +2767,7 @@
       </c>
     </row>
     <row r="196" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A196" t="inlineStr">
+      <c r="A196" s="8" t="inlineStr">
         <is>
           <t>Mobius Investment Trust plc</t>
         </is>
@@ -2779,7 +2779,7 @@
       </c>
     </row>
     <row r="197" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A197" t="inlineStr">
+      <c r="A197" s="8" t="inlineStr">
         <is>
           <t>Molten Ventures plc</t>
         </is>
@@ -2791,7 +2791,7 @@
       </c>
     </row>
     <row r="198" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A198" t="inlineStr">
+      <c r="A198" s="8" t="inlineStr">
         <is>
           <t>Molten Ventures VCT plc</t>
         </is>
@@ -2803,7 +2803,7 @@
       </c>
     </row>
     <row r="199" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A199" t="inlineStr">
+      <c r="A199" s="8" t="inlineStr">
         <is>
           <t>Monks Investment Trust plc</t>
         </is>
@@ -2815,7 +2815,7 @@
       </c>
     </row>
     <row r="200" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A200" t="inlineStr">
+      <c r="A200" s="8" t="inlineStr">
         <is>
           <t>Montanaro European Smaller Companies Trust plc</t>
         </is>
@@ -2827,7 +2827,7 @@
       </c>
     </row>
     <row r="201" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A201" t="inlineStr">
+      <c r="A201" s="8" t="inlineStr">
         <is>
           <t>Montanaro Uk Smaller Cos Investment Trust plc</t>
         </is>
@@ -2839,7 +2839,7 @@
       </c>
     </row>
     <row r="202" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A202" t="inlineStr">
+      <c r="A202" s="8" t="inlineStr">
         <is>
           <t>Murray Income Trust plc</t>
         </is>
@@ -2851,7 +2851,7 @@
       </c>
     </row>
     <row r="203" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A203" t="inlineStr">
+      <c r="A203" s="8" t="inlineStr">
         <is>
           <t>Murray International Trust plc</t>
         </is>
@@ -2863,7 +2863,7 @@
       </c>
     </row>
     <row r="204" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A204" t="inlineStr">
+      <c r="A204" s="8" t="inlineStr">
         <is>
           <t>NB Private Equity Partners Ltd</t>
         </is>
@@ -2875,7 +2875,7 @@
       </c>
     </row>
     <row r="205" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A205" t="inlineStr">
+      <c r="A205" s="8" t="inlineStr">
         <is>
           <t>New Star Investment Trust plc</t>
         </is>
@@ -2887,7 +2887,7 @@
       </c>
     </row>
     <row r="206" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A206" t="inlineStr">
+      <c r="A206" s="8" t="inlineStr">
         <is>
           <t>NextEnergy Solar Fund Ltd</t>
         </is>
@@ -2899,7 +2899,7 @@
       </c>
     </row>
     <row r="207" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A207" t="inlineStr">
+      <c r="A207" s="8" t="inlineStr">
         <is>
           <t>Nippon Active Value Fund plc</t>
         </is>
@@ -2911,7 +2911,7 @@
       </c>
     </row>
     <row r="208" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A208" t="inlineStr">
+      <c r="A208" s="8" t="inlineStr">
         <is>
           <t>North American Income Trust plc</t>
         </is>
@@ -2923,7 +2923,7 @@
       </c>
     </row>
     <row r="209" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A209" t="inlineStr">
+      <c r="A209" s="8" t="inlineStr">
         <is>
           <t>North Atlantic Smaller Cos Inv Tst plc</t>
         </is>
@@ -2935,7 +2935,7 @@
       </c>
     </row>
     <row r="210" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A210" t="inlineStr">
+      <c r="A210" s="8" t="inlineStr">
         <is>
           <t>Northern 2 VCT plc</t>
         </is>
@@ -2947,7 +2947,7 @@
       </c>
     </row>
     <row r="211" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A211" t="inlineStr">
+      <c r="A211" s="8" t="inlineStr">
         <is>
           <t>Northern 3 VCT plc</t>
         </is>
@@ -2959,7 +2959,7 @@
       </c>
     </row>
     <row r="212" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A212" t="inlineStr">
+      <c r="A212" s="8" t="inlineStr">
         <is>
           <t>Northern Venture Trust plc</t>
         </is>
@@ -2971,7 +2971,7 @@
       </c>
     </row>
     <row r="213" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A213" t="inlineStr">
+      <c r="A213" s="8" t="inlineStr">
         <is>
           <t>Oakley Capital Investments Ltd</t>
         </is>
@@ -2983,7 +2983,7 @@
       </c>
     </row>
     <row r="214" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A214" t="inlineStr">
+      <c r="A214" s="8" t="inlineStr">
         <is>
           <t>Oberon AIM VCT Plc</t>
         </is>
@@ -2995,7 +2995,7 @@
       </c>
     </row>
     <row r="215" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A215" t="inlineStr">
+      <c r="A215" s="8" t="inlineStr">
         <is>
           <t>Octopus AIM VCT 2 plc</t>
         </is>
@@ -3007,7 +3007,7 @@
       </c>
     </row>
     <row r="216" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A216" t="inlineStr">
+      <c r="A216" s="8" t="inlineStr">
         <is>
           <t>Octopus AIM VCT plc</t>
         </is>
@@ -3019,7 +3019,7 @@
       </c>
     </row>
     <row r="217" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A217" t="inlineStr">
+      <c r="A217" s="8" t="inlineStr">
         <is>
           <t>Octopus Apollo VCT plc</t>
         </is>
@@ -3031,7 +3031,7 @@
       </c>
     </row>
     <row r="218" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A218" t="inlineStr">
+      <c r="A218" s="8" t="inlineStr">
         <is>
           <t>Octopus Future Generations VCT plc</t>
         </is>
@@ -3043,7 +3043,7 @@
       </c>
     </row>
     <row r="219" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A219" t="inlineStr">
+      <c r="A219" s="8" t="inlineStr">
         <is>
           <t>Octopus Renewables Infrastructure Trust plc</t>
         </is>
@@ -3055,7 +3055,7 @@
       </c>
     </row>
     <row r="220" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A220" t="inlineStr">
+      <c r="A220" s="8" t="inlineStr">
         <is>
           <t>Octopus Titan VCT plc</t>
         </is>
@@ -3067,7 +3067,7 @@
       </c>
     </row>
     <row r="221" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A221" t="inlineStr">
+      <c r="A221" s="8" t="inlineStr">
         <is>
           <t>Odyssean Investment Trust plc</t>
         </is>
@@ -3079,7 +3079,7 @@
       </c>
     </row>
     <row r="222" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A222" t="inlineStr">
+      <c r="A222" s="8" t="inlineStr">
         <is>
           <t>Onward Opportunities Ltd</t>
         </is>
@@ -3091,7 +3091,7 @@
       </c>
     </row>
     <row r="223" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A223" t="inlineStr">
+      <c r="A223" s="8" t="inlineStr">
         <is>
           <t>Oryx International Growth Fund</t>
         </is>
@@ -3103,7 +3103,7 @@
       </c>
     </row>
     <row r="224" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A224" t="inlineStr">
+      <c r="A224" s="8" t="inlineStr">
         <is>
           <t>Oxford Technology 2</t>
         </is>
@@ -3115,7 +3115,7 @@
       </c>
     </row>
     <row r="225" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A225" t="inlineStr">
+      <c r="A225" s="8" t="inlineStr">
         <is>
           <t>Oxford Technology 2</t>
         </is>
@@ -3127,7 +3127,7 @@
       </c>
     </row>
     <row r="226" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A226" t="inlineStr">
+      <c r="A226" s="8" t="inlineStr">
         <is>
           <t>Oxford Technology 2</t>
         </is>
@@ -3139,7 +3139,7 @@
       </c>
     </row>
     <row r="227" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A227" t="inlineStr">
+      <c r="A227" s="8" t="inlineStr">
         <is>
           <t>Oxford Technology 2 VCT plc</t>
         </is>
@@ -3151,7 +3151,7 @@
       </c>
     </row>
     <row r="228" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A228" t="inlineStr">
+      <c r="A228" s="8" t="inlineStr">
         <is>
           <t>Pacific Assets Trust plc</t>
         </is>
@@ -3163,7 +3163,7 @@
       </c>
     </row>
     <row r="229" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A229" t="inlineStr">
+      <c r="A229" s="8" t="inlineStr">
         <is>
           <t>Pacific Horizon Investment Trust plc</t>
         </is>
@@ -3175,7 +3175,7 @@
       </c>
     </row>
     <row r="230" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A230" t="inlineStr">
+      <c r="A230" s="8" t="inlineStr">
         <is>
           <t>Pantheon Infrastructure Plc</t>
         </is>
@@ -3187,7 +3187,7 @@
       </c>
     </row>
     <row r="231" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A231" t="inlineStr">
+      <c r="A231" s="8" t="inlineStr">
         <is>
           <t>Pantheon International Plc</t>
         </is>
@@ -3199,7 +3199,7 @@
       </c>
     </row>
     <row r="232" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A232" t="inlineStr">
+      <c r="A232" s="8" t="inlineStr">
         <is>
           <t>Partners Group Private Equity</t>
         </is>
@@ -3211,7 +3211,7 @@
       </c>
     </row>
     <row r="233" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A233" t="inlineStr">
+      <c r="A233" s="8" t="inlineStr">
         <is>
           <t>Partners Group Private Equity Ltd</t>
         </is>
@@ -3223,7 +3223,7 @@
       </c>
     </row>
     <row r="234" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A234" t="inlineStr">
+      <c r="A234" s="8" t="inlineStr">
         <is>
           <t>Patria Private Equity Trust Plc</t>
         </is>
@@ -3235,7 +3235,7 @@
       </c>
     </row>
     <row r="235" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A235" t="inlineStr">
+      <c r="A235" s="8" t="inlineStr">
         <is>
           <t>Pembroke VCT plc</t>
         </is>
@@ -3247,7 +3247,7 @@
       </c>
     </row>
     <row r="236" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A236" t="inlineStr">
+      <c r="A236" s="8" t="inlineStr">
         <is>
           <t>Pershing Square Holdings Ltd</t>
         </is>
@@ -3259,7 +3259,7 @@
       </c>
     </row>
     <row r="237" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A237" t="inlineStr">
+      <c r="A237" s="8" t="inlineStr">
         <is>
           <t>Personal Assets Trust plc</t>
         </is>
@@ -3271,7 +3271,7 @@
       </c>
     </row>
     <row r="238" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A238" t="inlineStr">
+      <c r="A238" s="8" t="inlineStr">
         <is>
           <t>Phoenix Spree Deutschland Ltd</t>
         </is>
@@ -3283,7 +3283,7 @@
       </c>
     </row>
     <row r="239" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A239" t="inlineStr">
+      <c r="A239" s="8" t="inlineStr">
         <is>
           <t>Polar Capital Global Financials Trust plc</t>
         </is>
@@ -3295,7 +3295,7 @@
       </c>
     </row>
     <row r="240" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A240" t="inlineStr">
+      <c r="A240" s="8" t="inlineStr">
         <is>
           <t>Polar Capital Global Healthcare Trust plc</t>
         </is>
@@ -3307,7 +3307,7 @@
       </c>
     </row>
     <row r="241" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A241" t="inlineStr">
+      <c r="A241" s="8" t="inlineStr">
         <is>
           <t>Polar Capital Technology Trust plc</t>
         </is>
@@ -3319,7 +3319,7 @@
       </c>
     </row>
     <row r="242" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A242" t="inlineStr">
+      <c r="A242" s="8" t="inlineStr">
         <is>
           <t>Praetura Growth VCT plc</t>
         </is>
@@ -3331,7 +3331,7 @@
       </c>
     </row>
     <row r="243" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A243" t="inlineStr">
+      <c r="A243" s="8" t="inlineStr">
         <is>
           <t>Proven Growth &amp; Income VCT plc</t>
         </is>
@@ -3343,7 +3343,7 @@
       </c>
     </row>
     <row r="244" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A244" t="inlineStr">
+      <c r="A244" s="8" t="inlineStr">
         <is>
           <t>ProVen VCT plc</t>
         </is>
@@ -3355,7 +3355,7 @@
       </c>
     </row>
     <row r="245" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A245" t="inlineStr">
+      <c r="A245" s="8" t="inlineStr">
         <is>
           <t>Puma AIM VCT</t>
         </is>
@@ -3367,7 +3367,7 @@
       </c>
     </row>
     <row r="246" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A246" t="inlineStr">
+      <c r="A246" s="8" t="inlineStr">
         <is>
           <t>Puma Alpha VCT plc</t>
         </is>
@@ -3379,7 +3379,7 @@
       </c>
     </row>
     <row r="247" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A247" t="inlineStr">
+      <c r="A247" s="8" t="inlineStr">
         <is>
           <t>Puma VCT 13 Plc</t>
         </is>
@@ -3391,7 +3391,7 @@
       </c>
     </row>
     <row r="248" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A248" t="inlineStr">
+      <c r="A248" s="8" t="inlineStr">
         <is>
           <t>Real Estate Credit Investments Ltd</t>
         </is>
@@ -3403,7 +3403,7 @@
       </c>
     </row>
     <row r="249" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A249" t="inlineStr">
+      <c r="A249" s="8" t="inlineStr">
         <is>
           <t>Regional REIT Ltd</t>
         </is>
@@ -3415,7 +3415,7 @@
       </c>
     </row>
     <row r="250" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A250" t="inlineStr">
+      <c r="A250" s="8" t="inlineStr">
         <is>
           <t>Residential Secure Income REIT</t>
         </is>
@@ -3427,7 +3427,7 @@
       </c>
     </row>
     <row r="251" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A251" t="inlineStr">
+      <c r="A251" s="8" t="inlineStr">
         <is>
           <t>Rights &amp; Issues Investment Trust plc</t>
         </is>
@@ -3439,7 +3439,7 @@
       </c>
     </row>
     <row r="252" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A252" t="inlineStr">
+      <c r="A252" s="8" t="inlineStr">
         <is>
           <t>RIT Capital Partners plc</t>
         </is>
@@ -3451,7 +3451,7 @@
       </c>
     </row>
     <row r="253" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A253" t="inlineStr">
+      <c r="A253" s="8" t="inlineStr">
         <is>
           <t>River UK Micro Cap Red</t>
         </is>
@@ -3463,7 +3463,7 @@
       </c>
     </row>
     <row r="254" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A254" t="inlineStr">
+      <c r="A254" s="8" t="inlineStr">
         <is>
           <t>Riverstone Energy Ltd</t>
         </is>
@@ -3475,7 +3475,7 @@
       </c>
     </row>
     <row r="255" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A255" t="inlineStr">
+      <c r="A255" s="8" t="inlineStr">
         <is>
           <t>RM Infrastructure Income plc</t>
         </is>
@@ -3487,7 +3487,7 @@
       </c>
     </row>
     <row r="256" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A256" t="inlineStr">
+      <c r="A256" s="8" t="inlineStr">
         <is>
           <t>Rockwood Strategic Plc</t>
         </is>
@@ -3499,7 +3499,7 @@
       </c>
     </row>
     <row r="257" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A257" t="inlineStr">
+      <c r="A257" s="8" t="inlineStr">
         <is>
           <t>RTW Biotech Opportunities Ltd</t>
         </is>
@@ -3511,7 +3511,7 @@
       </c>
     </row>
     <row r="258" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A258" t="inlineStr">
+      <c r="A258" s="8" t="inlineStr">
         <is>
           <t>Ruffer Investment Co Ltd</t>
         </is>
@@ -3523,7 +3523,7 @@
       </c>
     </row>
     <row r="259" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A259" t="inlineStr">
+      <c r="A259" s="8" t="inlineStr">
         <is>
           <t>Schiehallion Fund Limited</t>
         </is>
@@ -3535,7 +3535,7 @@
       </c>
     </row>
     <row r="260" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A260" t="inlineStr">
+      <c r="A260" s="8" t="inlineStr">
         <is>
           <t>Schroder Asia Pacific Fund</t>
         </is>
@@ -3547,7 +3547,7 @@
       </c>
     </row>
     <row r="261" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A261" t="inlineStr">
+      <c r="A261" s="8" t="inlineStr">
         <is>
           <t>Schroder Asian Total Return Investment Company plc</t>
         </is>
@@ -3559,7 +3559,7 @@
       </c>
     </row>
     <row r="262" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A262" t="inlineStr">
+      <c r="A262" s="8" t="inlineStr">
         <is>
           <t>Schroder British Opportunities Trust</t>
         </is>
@@ -3571,7 +3571,7 @@
       </c>
     </row>
     <row r="263" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A263" t="inlineStr">
+      <c r="A263" s="8" t="inlineStr">
         <is>
           <t>Schroder BSC Social Impact Trust plc</t>
         </is>
@@ -3583,7 +3583,7 @@
       </c>
     </row>
     <row r="264" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A264" t="inlineStr">
+      <c r="A264" s="8" t="inlineStr">
         <is>
           <t>Schroder European Real Estate Investment Trust plc</t>
         </is>
@@ -3595,7 +3595,7 @@
       </c>
     </row>
     <row r="265" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A265" t="inlineStr">
+      <c r="A265" s="8" t="inlineStr">
         <is>
           <t>Schroder Income Growth Fund plc</t>
         </is>
@@ -3607,7 +3607,7 @@
       </c>
     </row>
     <row r="266" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A266" t="inlineStr">
+      <c r="A266" s="8" t="inlineStr">
         <is>
           <t>Schroder Japan Trust plc</t>
         </is>
@@ -3619,7 +3619,7 @@
       </c>
     </row>
     <row r="267" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A267" t="inlineStr">
+      <c r="A267" s="8" t="inlineStr">
         <is>
           <t>Schroder Oriental Income Fund</t>
         </is>
@@ -3631,7 +3631,7 @@
       </c>
     </row>
     <row r="268" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A268" t="inlineStr">
+      <c r="A268" s="8" t="inlineStr">
         <is>
           <t>Schroder Real Estate Investment Trust Ltd</t>
         </is>
@@ -3643,7 +3643,7 @@
       </c>
     </row>
     <row r="269" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A269" t="inlineStr">
+      <c r="A269" s="8" t="inlineStr">
         <is>
           <t>Schroder UK Mid Cap Fund plc</t>
         </is>
@@ -3655,7 +3655,7 @@
       </c>
     </row>
     <row r="270" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A270" t="inlineStr">
+      <c r="A270" s="8" t="inlineStr">
         <is>
           <t>Schroders Capital Global Innovation Trust</t>
         </is>
@@ -3667,7 +3667,7 @@
       </c>
     </row>
     <row r="271" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A271" t="inlineStr">
+      <c r="A271" s="8" t="inlineStr">
         <is>
           <t>Scottish American Investment Co plc</t>
         </is>
@@ -3679,7 +3679,7 @@
       </c>
     </row>
     <row r="272" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A272" t="inlineStr">
+      <c r="A272" s="8" t="inlineStr">
         <is>
           <t>Scottish Mortgage Investment Trust plc</t>
         </is>
@@ -3691,7 +3691,7 @@
       </c>
     </row>
     <row r="273" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A273" t="inlineStr">
+      <c r="A273" s="8" t="inlineStr">
         <is>
           <t>Scottish Oriental Smaller Companies Trust plc</t>
         </is>
@@ -3703,7 +3703,7 @@
       </c>
     </row>
     <row r="274" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A274" t="inlineStr">
+      <c r="A274" s="8" t="inlineStr">
         <is>
           <t>SDCL Efficiency Income Trust Plc</t>
         </is>
@@ -3715,7 +3715,7 @@
       </c>
     </row>
     <row r="275" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A275" t="inlineStr">
+      <c r="A275" s="8" t="inlineStr">
         <is>
           <t>Seed Innovations Limited</t>
         </is>
@@ -3727,7 +3727,7 @@
       </c>
     </row>
     <row r="276" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A276" t="inlineStr">
+      <c r="A276" s="8" t="inlineStr">
         <is>
           <t>Seneca Growth Capital VCT plc</t>
         </is>
@@ -3739,7 +3739,7 @@
       </c>
     </row>
     <row r="277" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A277" t="inlineStr">
+      <c r="A277" s="8" t="inlineStr">
         <is>
           <t>Seneca Growth Capital VCT Plc</t>
         </is>
@@ -3751,7 +3751,7 @@
       </c>
     </row>
     <row r="278" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A278" t="inlineStr">
+      <c r="A278" s="8" t="inlineStr">
         <is>
           <t>Sequoia Economic Infrastructure Income Fund Ltd</t>
         </is>
@@ -3763,7 +3763,7 @@
       </c>
     </row>
     <row r="279" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A279" t="inlineStr">
+      <c r="A279" s="8" t="inlineStr">
         <is>
           <t>Seraphim Space Investment Trust plc</t>
         </is>
@@ -3775,7 +3775,7 @@
       </c>
     </row>
     <row r="280" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A280" t="inlineStr">
+      <c r="A280" s="8" t="inlineStr">
         <is>
           <t>Sherborne Investors C</t>
         </is>
@@ -3787,7 +3787,7 @@
       </c>
     </row>
     <row r="281" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A281" t="inlineStr">
+      <c r="A281" s="8" t="inlineStr">
         <is>
           <t>Social Housing REIT Plc</t>
         </is>
@@ -3799,7 +3799,7 @@
       </c>
     </row>
     <row r="282" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A282" t="inlineStr">
+      <c r="A282" s="8" t="inlineStr">
         <is>
           <t>Strategic Equity Capital plc</t>
         </is>
@@ -3811,7 +3811,7 @@
       </c>
     </row>
     <row r="283" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A283" t="inlineStr">
+      <c r="A283" s="8" t="inlineStr">
         <is>
           <t>STS Global Income &amp; Growth Trust plc</t>
         </is>
@@ -3823,7 +3823,7 @@
       </c>
     </row>
     <row r="284" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A284" t="inlineStr">
+      <c r="A284" s="8" t="inlineStr">
         <is>
           <t>Symphony International Holdings Ltd</t>
         </is>
@@ -3835,7 +3835,7 @@
       </c>
     </row>
     <row r="285" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A285" t="inlineStr">
+      <c r="A285" s="8" t="inlineStr">
         <is>
           <t>Syncona Limited</t>
         </is>
@@ -3847,7 +3847,7 @@
       </c>
     </row>
     <row r="286" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A286" t="inlineStr">
+      <c r="A286" s="8" t="inlineStr">
         <is>
           <t>Target Healthcare REIT plc</t>
         </is>
@@ -3859,7 +3859,7 @@
       </c>
     </row>
     <row r="287" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A287" t="inlineStr">
+      <c r="A287" s="8" t="inlineStr">
         <is>
           <t>Temple Bar Investment Trust plc</t>
         </is>
@@ -3871,7 +3871,7 @@
       </c>
     </row>
     <row r="288" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A288" t="inlineStr">
+      <c r="A288" s="8" t="inlineStr">
         <is>
           <t>Templeton Emerging Markets Investment Trust plc</t>
         </is>
@@ -3883,7 +3883,7 @@
       </c>
     </row>
     <row r="289" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A289" t="inlineStr">
+      <c r="A289" s="8" t="inlineStr">
         <is>
           <t>Tetragon Financial Group Ltd</t>
         </is>
@@ -3895,7 +3895,7 @@
       </c>
     </row>
     <row r="290" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A290" t="inlineStr">
+      <c r="A290" s="8" t="inlineStr">
         <is>
           <t>Tetragon Financial Group Ltd</t>
         </is>
@@ -3907,7 +3907,7 @@
       </c>
     </row>
     <row r="291" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A291" t="inlineStr">
+      <c r="A291" s="8" t="inlineStr">
         <is>
           <t>The European Smaller Companies Trust plc</t>
         </is>
@@ -3919,7 +3919,7 @@
       </c>
     </row>
     <row r="292" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A292" t="inlineStr">
+      <c r="A292" s="8" t="inlineStr">
         <is>
           <t>The Global Smaller Companies Trust Plc</t>
         </is>
@@ -3931,7 +3931,7 @@
       </c>
     </row>
     <row r="293" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A293" t="inlineStr">
+      <c r="A293" s="8" t="inlineStr">
         <is>
           <t>The Renewables Infrastructure Group Limited</t>
         </is>
@@ -3943,7 +3943,7 @@
       </c>
     </row>
     <row r="294" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A294" t="inlineStr">
+      <c r="A294" s="8" t="inlineStr">
         <is>
           <t>TR Property Investment Trust plc</t>
         </is>
@@ -3955,7 +3955,7 @@
       </c>
     </row>
     <row r="295" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A295" t="inlineStr">
+      <c r="A295" s="8" t="inlineStr">
         <is>
           <t>Triple Point VCT 2011 Plc</t>
         </is>
@@ -3967,7 +3967,7 @@
       </c>
     </row>
     <row r="296" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A296" t="inlineStr">
+      <c r="A296" s="8" t="inlineStr">
         <is>
           <t>Tritax Big Box REIT plc</t>
         </is>
@@ -3979,7 +3979,7 @@
       </c>
     </row>
     <row r="297" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A297" t="inlineStr">
+      <c r="A297" s="8" t="inlineStr">
         <is>
           <t>Tufton Assets Limited</t>
         </is>
@@ -3991,7 +3991,7 @@
       </c>
     </row>
     <row r="298" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A298" t="inlineStr">
+      <c r="A298" s="8" t="inlineStr">
         <is>
           <t>TwentyFour Income Fund Ltd</t>
         </is>
@@ -4003,7 +4003,7 @@
       </c>
     </row>
     <row r="299" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A299" t="inlineStr">
+      <c r="A299" s="8" t="inlineStr">
         <is>
           <t>TwentyFour Select Monthly Income Fund Limited</t>
         </is>
@@ -4015,7 +4015,7 @@
       </c>
     </row>
     <row r="300" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A300" t="inlineStr">
+      <c r="A300" s="8" t="inlineStr">
         <is>
           <t>Unicorn AIM VCT plc</t>
         </is>
@@ -4027,7 +4027,7 @@
       </c>
     </row>
     <row r="301" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A301" t="inlineStr">
+      <c r="A301" s="8" t="inlineStr">
         <is>
           <t>US Solar Fund Plc</t>
         </is>
@@ -4039,7 +4039,7 @@
       </c>
     </row>
     <row r="302" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A302" t="inlineStr">
+      <c r="A302" s="8" t="inlineStr">
         <is>
           <t>Utilico Emerging Markets Trust plc</t>
         </is>
@@ -4051,7 +4051,7 @@
       </c>
     </row>
     <row r="303" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A303" t="inlineStr">
+      <c r="A303" s="8" t="inlineStr">
         <is>
           <t>Value and Indexed Property Income Trust</t>
         </is>
@@ -4063,7 +4063,7 @@
       </c>
     </row>
     <row r="304" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A304" t="inlineStr">
+      <c r="A304" s="8" t="inlineStr">
         <is>
           <t>VH Global Energy Infrastructure Plc</t>
         </is>
@@ -4075,7 +4075,7 @@
       </c>
     </row>
     <row r="305" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A305" t="inlineStr">
+      <c r="A305" s="8" t="inlineStr">
         <is>
           <t>Vietnam Enterprise Investments Ltd</t>
         </is>
@@ -4087,7 +4087,7 @@
       </c>
     </row>
     <row r="306" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A306" t="inlineStr">
+      <c r="A306" s="8" t="inlineStr">
         <is>
           <t>VinaCapital Vietnam Opportunity Fund Ltd</t>
         </is>
@@ -4099,7 +4099,7 @@
       </c>
     </row>
     <row r="307" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A307" t="inlineStr">
+      <c r="A307" s="8" t="inlineStr">
         <is>
           <t>Volta Finance Ltd</t>
         </is>
@@ -4111,7 +4111,7 @@
       </c>
     </row>
     <row r="308" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A308" t="inlineStr">
+      <c r="A308" s="8" t="inlineStr">
         <is>
           <t>Volta Finance Ltd</t>
         </is>
@@ -4123,7 +4123,7 @@
       </c>
     </row>
     <row r="309" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A309" t="inlineStr">
+      <c r="A309" s="8" t="inlineStr">
         <is>
           <t>VPC Specialty Lending Investments plc</t>
         </is>
@@ -4135,7 +4135,7 @@
       </c>
     </row>
     <row r="310" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A310" t="inlineStr">
+      <c r="A310" s="8" t="inlineStr">
         <is>
           <t>Worldwide Healthcare Trust plc</t>
         </is>
@@ -4147,7 +4147,7 @@
       </c>
     </row>
     <row r="311" ht="18" customFormat="1" customHeight="1" s="8">
-      <c r="A311" t="inlineStr">
+      <c r="A311" s="8" t="inlineStr">
         <is>
           <t>Worsley Investors Limited</t>
         </is>

--- a/spreadsheet/hl.xlsx
+++ b/spreadsheet/hl.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -469,7 +469,39 @@
         </is>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Oxford Technology 2</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BN73FN0/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Oxford Technology 2</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BN73FM9/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C225" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C226" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/spreadsheet/hl.xlsx
+++ b/spreadsheet/hl.xlsx
@@ -475,13 +475,11 @@
           <t>Oxford Technology 2</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr"/>
       <c r="C225" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/shares/shares-search-results/BN73FN0/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -489,13 +487,11 @@
           <t>Oxford Technology 2</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr"/>
       <c r="C226" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/shares/shares-search-results/BN73FM9/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -512,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D1397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -543,7 +539,351 @@
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Europe Quality Income UCITS ETF Inc</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BFWY9Q3/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>USD Floating Rate Bond UCITS ETF Hedged (Dist)</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr"/>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/404/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>MSCI EM IMI ESG Screened UCITS ETF USD Acc</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr"/>
+      <c r="C602" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BFNM3P3/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>MSCI EM IMI ESG Screened UCITS ETF USD Dis</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr"/>
+      <c r="C603" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BFNM3N1/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr"/>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Global High Yield Corp Bond UCITS ETF Dist</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr"/>
+      <c r="C682" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B74DQ49/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr"/>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>MSCI Eastern Europe Capped UCITS ETF (Dist) USD</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr"/>
+      <c r="C692" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B1CDHR9/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr"/>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>USD Corp Bond Interest Rate Hedged UCITS ETF Dist</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr"/>
+      <c r="C715" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BCLWRB8/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr"/>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>USD Corp Bond Interest Rate Hedged UCITS ETF Dist</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr"/>
+      <c r="C716" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BCLWRB8/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr"/>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>MSCI Russia ADR/GDR UCITS ETF</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr"/>
+      <c r="C807" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B5V8739/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr"/>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>Factor MSCI USA Prime Value Screened UCITS ETF USD</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr"/>
+      <c r="C1045" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BYTLLR5/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr"/>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>Factor MSCI USA Quality Screened UCITS ETF hGBP di</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr"/>
+      <c r="C1046" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BYYK2M9/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr"/>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>MSCI USA Socially Responsible UCITS ETF hGBP dis (</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr"/>
+      <c r="C1057" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BJXT3H4/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr"/>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>BBG MSCI US Liquid Corp Sustainable UCITS ETF hGBP</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr"/>
+      <c r="C1067" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BDGSX43/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr"/>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>MSCI EMU Socially Responsible UCITS ETF EUR dis (G</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr"/>
+      <c r="C1091" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B7TLNN6/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr"/>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>MSCI USA Socially Responsible UCITS ETF USD dis (G</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr"/>
+      <c r="C1099" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B6YRHS5/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr"/>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>MSCI World Socially Responsible UCITS ETF USD dis</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr"/>
+      <c r="C1100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B8NZ739/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr"/>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>MSCI Emerging Markets Index UCITS ETF</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr"/>
+      <c r="C1284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B24CWV0/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr"/>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>MSCI Japan ESG Screened UCITS ETF 2D GBP Hedged</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr"/>
+      <c r="C1304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/404/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr"/>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 UCITS ETF</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr"/>
+      <c r="C1362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/404/company-information/company-information/company-information</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr"/>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>Germany Government Bond UCITS ETF 1D</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>LU0468896575</t>
+        </is>
+      </c>
+      <c r="C1395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/x/xtrackers-ii-germany-government-bond-ucits/company-information</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr"/>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>Global Inflation-Linked Bond UCITS ETF 1C EUR Hdg</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>LU0290357929</t>
+        </is>
+      </c>
+      <c r="C1396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/x/xtrackers-ii-global-inflation-linked-bond/company-information</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr"/>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>MSCI World ex USA UCITS ETF 1C</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>IE0006WW1TQ4</t>
+        </is>
+      </c>
+      <c r="C1397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/x/xtrackers-msci-world-ex-usa-ucits-etf-1c/company-information</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr"/>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C478" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C602" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C603" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C682" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C692" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C715" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C716" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C807" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1045" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1046" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1057" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1067" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1091" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1099" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1100" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1284" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1304" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1362" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1395" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1396" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1397" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/spreadsheet/hl.xlsx
+++ b/spreadsheet/hl.xlsx
@@ -545,13 +545,11 @@
           <t>Europe Quality Income UCITS ETF Inc</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/shares/shares-search-results/BFWY9Q3/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -559,13 +557,11 @@
           <t>USD Floating Rate Bond UCITS ETF Hedged (Dist)</t>
         </is>
       </c>
-      <c r="B478" t="inlineStr"/>
       <c r="C478" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/404/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -573,13 +569,11 @@
           <t>MSCI EM IMI ESG Screened UCITS ETF USD Acc</t>
         </is>
       </c>
-      <c r="B602" t="inlineStr"/>
       <c r="C602" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/shares/shares-search-results/BFNM3P3/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -587,13 +581,11 @@
           <t>MSCI EM IMI ESG Screened UCITS ETF USD Dis</t>
         </is>
       </c>
-      <c r="B603" t="inlineStr"/>
       <c r="C603" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/shares/shares-search-results/BFNM3N1/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D603" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -601,13 +593,11 @@
           <t>Global High Yield Corp Bond UCITS ETF Dist</t>
         </is>
       </c>
-      <c r="B682" t="inlineStr"/>
       <c r="C682" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/shares/shares-search-results/B74DQ49/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D682" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -615,13 +605,11 @@
           <t>MSCI Eastern Europe Capped UCITS ETF (Dist) USD</t>
         </is>
       </c>
-      <c r="B692" t="inlineStr"/>
       <c r="C692" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/shares/shares-search-results/B1CDHR9/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D692" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -629,13 +617,11 @@
           <t>USD Corp Bond Interest Rate Hedged UCITS ETF Dist</t>
         </is>
       </c>
-      <c r="B715" t="inlineStr"/>
       <c r="C715" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/shares/shares-search-results/BCLWRB8/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D715" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -643,13 +629,11 @@
           <t>USD Corp Bond Interest Rate Hedged UCITS ETF Dist</t>
         </is>
       </c>
-      <c r="B716" t="inlineStr"/>
       <c r="C716" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/shares/shares-search-results/BCLWRB8/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D716" t="inlineStr"/>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
@@ -657,13 +641,11 @@
           <t>MSCI Russia ADR/GDR UCITS ETF</t>
         </is>
       </c>
-      <c r="B807" t="inlineStr"/>
       <c r="C807" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/shares/shares-search-results/B5V8739/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D807" t="inlineStr"/>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
@@ -671,13 +653,11 @@
           <t>Factor MSCI USA Prime Value Screened UCITS ETF USD</t>
         </is>
       </c>
-      <c r="B1045" t="inlineStr"/>
       <c r="C1045" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/shares/shares-search-results/BYTLLR5/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D1045" t="inlineStr"/>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
@@ -685,13 +665,11 @@
           <t>Factor MSCI USA Quality Screened UCITS ETF hGBP di</t>
         </is>
       </c>
-      <c r="B1046" t="inlineStr"/>
       <c r="C1046" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/shares/shares-search-results/BYYK2M9/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D1046" t="inlineStr"/>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
@@ -699,13 +677,11 @@
           <t>MSCI USA Socially Responsible UCITS ETF hGBP dis (</t>
         </is>
       </c>
-      <c r="B1057" t="inlineStr"/>
       <c r="C1057" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/shares/shares-search-results/BJXT3H4/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D1057" t="inlineStr"/>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
@@ -713,13 +689,11 @@
           <t>BBG MSCI US Liquid Corp Sustainable UCITS ETF hGBP</t>
         </is>
       </c>
-      <c r="B1067" t="inlineStr"/>
       <c r="C1067" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/shares/shares-search-results/BDGSX43/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D1067" t="inlineStr"/>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
@@ -727,13 +701,11 @@
           <t>MSCI EMU Socially Responsible UCITS ETF EUR dis (G</t>
         </is>
       </c>
-      <c r="B1091" t="inlineStr"/>
       <c r="C1091" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/shares/shares-search-results/B7TLNN6/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D1091" t="inlineStr"/>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
@@ -741,13 +713,11 @@
           <t>MSCI USA Socially Responsible UCITS ETF USD dis (G</t>
         </is>
       </c>
-      <c r="B1099" t="inlineStr"/>
       <c r="C1099" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/shares/shares-search-results/B6YRHS5/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D1099" t="inlineStr"/>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
@@ -755,13 +725,11 @@
           <t>MSCI World Socially Responsible UCITS ETF USD dis</t>
         </is>
       </c>
-      <c r="B1100" t="inlineStr"/>
       <c r="C1100" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/shares/shares-search-results/B8NZ739/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D1100" t="inlineStr"/>
     </row>
     <row r="1284">
       <c r="A1284" t="inlineStr">
@@ -769,13 +737,11 @@
           <t>MSCI Emerging Markets Index UCITS ETF</t>
         </is>
       </c>
-      <c r="B1284" t="inlineStr"/>
       <c r="C1284" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/shares/shares-search-results/B24CWV0/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D1284" t="inlineStr"/>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
@@ -783,13 +749,11 @@
           <t>MSCI Japan ESG Screened UCITS ETF 2D GBP Hedged</t>
         </is>
       </c>
-      <c r="B1304" t="inlineStr"/>
       <c r="C1304" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/404/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D1304" t="inlineStr"/>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
@@ -797,13 +761,11 @@
           <t>S&amp;P 500 UCITS ETF</t>
         </is>
       </c>
-      <c r="B1362" t="inlineStr"/>
       <c r="C1362" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/404/company-information/company-information/company-information</t>
         </is>
       </c>
-      <c r="D1362" t="inlineStr"/>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
@@ -821,7 +783,6 @@
           <t>https://www.hl.co.uk/shares/shares-search-results/x/xtrackers-ii-germany-government-bond-ucits/company-information</t>
         </is>
       </c>
-      <c r="D1395" t="inlineStr"/>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
@@ -839,7 +800,6 @@
           <t>https://www.hl.co.uk/shares/shares-search-results/x/xtrackers-ii-global-inflation-linked-bond/company-information</t>
         </is>
       </c>
-      <c r="D1396" t="inlineStr"/>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
@@ -857,7 +817,6 @@
           <t>https://www.hl.co.uk/shares/shares-search-results/x/xtrackers-msci-world-ex-usa-ucits-etf-1c/company-information</t>
         </is>
       </c>
-      <c r="D1397" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -12316,14 +12275,16 @@
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>CG Portfolio Fund</t>
-        </is>
-      </c>
+          <t>CG Real Return Class (GBP)</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr"/>
       <c r="C951" s="2" t="inlineStr">
         <is>
-          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/BG5Q6F1</t>
-        </is>
-      </c>
+          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/B00C0L6/key-features/key-features/key-features</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr"/>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
@@ -13408,14 +13369,16 @@
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>CT Latin America (Class Z)</t>
-        </is>
-      </c>
+          <t>CT Managed Bond (Class Z)</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr"/>
       <c r="C1042" s="2" t="inlineStr">
         <is>
-          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/B8BQ6V5</t>
-        </is>
-      </c>
+          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/t/threadneedle-managed-bond-class-z-accumulation/key-features/key-features/key-features</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr"/>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
@@ -18100,14 +18063,16 @@
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>FTGF ClearBridge US Eq Sustainability (X Hg)</t>
-        </is>
-      </c>
+          <t>FTGF ClearBridge Global Growth Leaders</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr"/>
       <c r="C1433" s="2" t="inlineStr">
         <is>
-          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/BL3NDQ9</t>
-        </is>
-      </c>
+          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/BTHZ4L9/key-features/key-features/key-features</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr"/>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
@@ -28372,26 +28337,30 @@
     <row r="2289">
       <c r="A2289" t="inlineStr">
         <is>
-          <t>Legal &amp; General Fut Wrld ESG Screened &amp; Sel Multi-</t>
-        </is>
-      </c>
+          <t>Legal &amp; General Fut Wrld ESG Screened &amp; Sel Mul In</t>
+        </is>
+      </c>
+      <c r="B2289" t="inlineStr"/>
       <c r="C2289" s="2" t="inlineStr">
         <is>
-          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/BJ0M398</t>
-        </is>
-      </c>
+          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/BMX5HR1/key-features/key-features/key-features</t>
+        </is>
+      </c>
+      <c r="D2289" t="inlineStr"/>
     </row>
     <row r="2290">
       <c r="A2290" t="inlineStr">
         <is>
-          <t>Legal &amp; General Fut Wrld ESG Tilted &amp; Opt Emg Mkt</t>
-        </is>
-      </c>
+          <t>Legal &amp; General Fut Wrld ESG Screened &amp; Sel Mul In</t>
+        </is>
+      </c>
+      <c r="B2290" t="inlineStr"/>
       <c r="C2290" s="2" t="inlineStr">
         <is>
-          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/BL6C1V4</t>
-        </is>
-      </c>
+          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/BMX5HS2/key-features/key-features/key-features</t>
+        </is>
+      </c>
+      <c r="D2290" t="inlineStr"/>
     </row>
     <row r="2291">
       <c r="A2291" t="inlineStr">
@@ -35320,14 +35289,16 @@
     <row r="2868">
       <c r="A2868" t="inlineStr">
         <is>
-          <t>Orbis Global Balanced (Standard Fee)</t>
-        </is>
-      </c>
+          <t>Overstone World All-Cap Equity (Class I)</t>
+        </is>
+      </c>
+      <c r="B2868" t="inlineStr"/>
       <c r="C2868" s="2" t="inlineStr">
         <is>
-          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/BJ02KY2</t>
-        </is>
-      </c>
+          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/BKF3JL7/key-features/key-features/key-features</t>
+        </is>
+      </c>
+      <c r="D2868" t="inlineStr"/>
     </row>
     <row r="2869">
       <c r="A2869" t="inlineStr">
@@ -37216,14 +37187,16 @@
     <row r="3026">
       <c r="A3026" t="inlineStr">
         <is>
-          <t>Premier Miton Diversified Bal Growth (Class D)</t>
-        </is>
-      </c>
+          <t>Premier Miton Diversified Responsible Growth</t>
+        </is>
+      </c>
+      <c r="B3026" t="inlineStr"/>
       <c r="C3026" s="2" t="inlineStr">
         <is>
-          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/BHNWGP8</t>
-        </is>
-      </c>
+          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/m/miton-balanced-multi-asset-accumulation2/key-features/key-features/key-features</t>
+        </is>
+      </c>
+      <c r="D3026" t="inlineStr"/>
     </row>
     <row r="3027">
       <c r="A3027" t="inlineStr">
@@ -40240,14 +40213,16 @@
     <row r="3278">
       <c r="A3278" t="inlineStr">
         <is>
-          <t>Sarasin Balanced Managed (P)</t>
-        </is>
-      </c>
+          <t>Sarasin Global Dividend P (GBP Hedged)</t>
+        </is>
+      </c>
+      <c r="B3278" t="inlineStr"/>
       <c r="C3278" s="2" t="inlineStr">
         <is>
-          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/BTRTNF8</t>
-        </is>
-      </c>
+          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/BLB2N02/key-features/key-features/key-features</t>
+        </is>
+      </c>
+      <c r="D3278" t="inlineStr"/>
     </row>
     <row r="3279">
       <c r="A3279" t="inlineStr">
@@ -40660,14 +40635,16 @@
     <row r="3313">
       <c r="A3313" t="inlineStr">
         <is>
-          <t>Schroder Asian Discovery (Class Z)</t>
-        </is>
-      </c>
+          <t>Schroder Blended Portfolio 6 (Class Z)</t>
+        </is>
+      </c>
+      <c r="B3313" t="inlineStr"/>
       <c r="C3313" s="2" t="inlineStr">
         <is>
-          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/B5ZS9V7</t>
-        </is>
-      </c>
+          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/BF77ZW5/key-features/key-features/key-features</t>
+        </is>
+      </c>
+      <c r="D3313" t="inlineStr"/>
     </row>
     <row r="3314">
       <c r="A3314" t="inlineStr">
@@ -41044,14 +41021,16 @@
     <row r="3345">
       <c r="A3345" t="inlineStr">
         <is>
-          <t>Schroder Global Emerging Markets (Class Z)</t>
-        </is>
-      </c>
+          <t>Schroder Global Innovation (Class C)</t>
+        </is>
+      </c>
+      <c r="B3345" t="inlineStr"/>
       <c r="C3345" s="2" t="inlineStr">
         <is>
-          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/B76V5Q6</t>
-        </is>
-      </c>
+          <t>https://www.hl.co.uk/funds/fund-discounts,-prices--and--factsheets/search-results/BGMGMQ7/key-features/key-features/key-features</t>
+        </is>
+      </c>
+      <c r="D3345" t="inlineStr"/>
     </row>
     <row r="3346">
       <c r="A3346" t="inlineStr">

--- a/spreadsheet/hl.xlsx
+++ b/spreadsheet/hl.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -469,7 +469,39 @@
         </is>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Oxford Technology 2</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BN73FN0/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Oxford Technology 2</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BN73FM9/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C225" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C226" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/spreadsheet/hl.xlsx
+++ b/spreadsheet/hl.xlsx
@@ -475,13 +475,11 @@
           <t>Oxford Technology 2</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr"/>
       <c r="C225" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/shares/shares-search-results/BN73FN0/company-information/company-information/company-information/key-features</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -489,13 +487,11 @@
           <t>Oxford Technology 2</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr"/>
       <c r="C226" s="2" t="inlineStr">
         <is>
           <t>https://www.hl.co.uk/shares/shares-search-results/BN73FM9/company-information/company-information/company-information/key-features</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -512,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D1362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -543,7 +539,294 @@
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Europe Quality Income UCITS ETF Inc</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BFWY9Q3/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>USD Floating Rate Bond UCITS ETF Hedged (Dist)</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr"/>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/404/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>MSCI EM IMI ESG Screened UCITS ETF USD Acc</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr"/>
+      <c r="C602" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BFNM3P3/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>MSCI EM IMI ESG Screened UCITS ETF USD Dis</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr"/>
+      <c r="C603" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BFNM3N1/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr"/>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Global High Yield Corp Bond UCITS ETF Dist</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr"/>
+      <c r="C682" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B74DQ49/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr"/>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>MSCI Eastern Europe Capped UCITS ETF (Dist) USD</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr"/>
+      <c r="C692" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B1CDHR9/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr"/>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>USD Corp Bond Interest Rate Hedged UCITS ETF Dist</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr"/>
+      <c r="C715" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BCLWRB8/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr"/>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>USD Corp Bond Interest Rate Hedged UCITS ETF Dist</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr"/>
+      <c r="C716" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BCLWRB8/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr"/>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>MSCI Russia ADR/GDR UCITS ETF</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr"/>
+      <c r="C807" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B5V8739/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr"/>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>Factor MSCI USA Prime Value Screened UCITS ETF USD</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr"/>
+      <c r="C1045" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BYTLLR5/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr"/>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>Factor MSCI USA Quality Screened UCITS ETF hGBP di</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr"/>
+      <c r="C1046" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BYYK2M9/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr"/>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>MSCI USA Socially Responsible UCITS ETF hGBP dis (</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr"/>
+      <c r="C1057" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BJXT3H4/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr"/>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>BBG MSCI US Liquid Corp Sustainable UCITS ETF hGBP</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr"/>
+      <c r="C1067" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BDGSX43/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr"/>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>MSCI EMU Socially Responsible UCITS ETF EUR dis (G</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr"/>
+      <c r="C1091" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B7TLNN6/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr"/>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>MSCI USA Socially Responsible UCITS ETF USD dis (G</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr"/>
+      <c r="C1099" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B6YRHS5/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr"/>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>MSCI World Socially Responsible UCITS ETF USD dis</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr"/>
+      <c r="C1100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B8NZ739/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr"/>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>MSCI Emerging Markets Index UCITS ETF</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr"/>
+      <c r="C1284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B24CWV0/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr"/>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>MSCI Japan ESG Screened UCITS ETF 2D GBP Hedged</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr"/>
+      <c r="C1304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/404/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr"/>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 UCITS ETF</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr"/>
+      <c r="C1362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/404/company-information/company-information/company-information/key-features</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr"/>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C478" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C602" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C603" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C682" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C692" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C715" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C716" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C807" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1045" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1046" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1057" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1067" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1091" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1099" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1100" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1284" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1304" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1362" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/spreadsheet/hl.xlsx
+++ b/spreadsheet/hl.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,13 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -57,15 +64,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -428,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -459,7 +469,3987 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>3i Group Plc</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B1YW440</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3i Infrastructure plc</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BF5FX16</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aberdeen Asia Focus Plc</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BMF19B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aberdeen Asian Income Fund Limited</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B0P6J83</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aberdeen Equity Income Trust Plc</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0603959</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Aberdeen New India Investmen Trust</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0604877</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Aberdeen UK Smaller Companies Growth Trust Plc</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0295958</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Aberforth Geared Value &amp; Income Trust Plc</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BPJMQ25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Aberforth Smaller Companies Trust plc</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0006655</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Abrdn Diversified Income &amp; Growth Trust</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0129756</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Abrdn European Logistics Income Plc</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BD9PXH4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Abrdn Property Income Trust Ltd</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/3387528</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Achilles Investment Company Limited</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BT3GKD0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AEW UK REIT plc</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BWD2415</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Albion Crown VCT Plc</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0257743</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Albion Enterprise VCT plc</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B1G3LR3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Albion Technology &amp; General VCT plc</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0558167</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Alliance Witan plc</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B11V7W9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Allianz Technology Trust plc</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BNG2M15</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Alternative Income REIT</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BDVK708</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Aquila European Renewables plc</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BJMXQK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Artemis UK Future Leaders plc</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B1FL3C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ashoka India Equity Inv Trust Plc</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BF50VS4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ashoka WhiteOak Emerging Markets Trust plc</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BMZR7D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Athelney Trust</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0060929</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Aurora UK Alpha Plc</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0063326</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AVI Global Trust plc</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BLH3CY6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AVI Japan Opportunity Trust Plc</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BD6H5D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Baillie Gifford China Growth Trust plc</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0365602</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Baillie Gifford European Growth Trust Plc</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BMC7T38</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Baillie Gifford Japan Trust plc</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0048583</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Baillie Gifford Shin Nippon plc</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BFXYH24</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Baillie Gifford UK Growth Trust plc</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0791348</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Baillie Gifford US Growth Trust plc</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BDFGHW4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Baker Steel Resources Trust Ltd</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B6686L2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bankers Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BN4NDR3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Barings Emerging EMEA Opportunities</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/3227334</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Baronsmead Second Venture Trust plc</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/3002810</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Baronsmead Venture Trust plc</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0263193</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BH Macro Ltd</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BQBFY36</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BH Macro Ltd</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BQBFY47</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BioPharma Credit plc</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BDGKMY2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BioPharma Credit Plc</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BP2NZ40</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Biotech Growth Trust plc (The)</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0038551</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Blackfinch plc</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BKV46W4</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BlackRock American Income Trust Plc</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B7W0XJ6</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BlackRock Energy And Resources Income Trust plc</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B0N8MF9</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BlackRock Frontiers Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B3SXM83</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BlackRock Greater Europe Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B01RDH7</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BlackRock Income &amp; Growth Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/3096169</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BlackRock Latin American Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0505840</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BlackRock Smaller Companies Trust plc</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0643610</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BlackRock World Mining Trust plc</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0577485</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Blue Star Capital plc</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BS6Y1X1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Bluefield Solar Income Fund Limited</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BB0RDB9</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>British &amp; American Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0065311</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>British Smaller Companies VCT plc</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0140315</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>British Smaller Companies VCT2 plc</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0500179</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Brown Advisory US Smaller Companies</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0346340</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Brunner Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0149000</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Calculus VCT plc</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BYQPF34</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Caledonia Investments plc</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BTNQ8K3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Canadian General Investments Ltd</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0170710</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Capital for Colleagues plc</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BGCZ2V9</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Capital Gearing Trust plc</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0173861</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Castelnau Group Ltd</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BMWWJM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>CC Japan Income &amp; Growth Trust plc</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BYSRMH1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Ceiba Investments Ltd</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BFMDJH1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Chelverton UK Dividend Trust plc</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0661582</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Chenavari Toro Income Fund Ltd</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BWBSDM9</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Chrysalis Investments Limited</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BGJYPP4</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>City Of London Investment Trust</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0199049</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Cordiant Digital Infrastructure Limited</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BMC7TM7</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>CQS Natural Resources Growth and Income plc</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0035392</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>CQS New City High Yield Fund Ltd</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B1LZS51</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Crystal Amber Fund Ltd</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B1Z2SL4</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>CT Global Managed Portfolio Trust plc</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B2PP252</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>CT Global Managed Portfolio Trust Plc</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B2PP3J3</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>CT Healthcare Trust plc</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BZCNLL9</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>CT Private Equity Trust Plc</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/3073827</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>CT UK Capital &amp; Income Inv Trust plc</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0346328</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>CT UK High Income Trust plc</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B1N4H59</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>CT UK High Income Trust plc</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B1N4G29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Custodian Property Income REIT plc</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BJFLFT4</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>CVC Income &amp; Growth Limited</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B9MRHZ5</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Develop North plc</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BD0ND66</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Digital 9 Infrastructure Plc</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BPH3HM7</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>DP Aircraft I Limited</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BBP6HP3</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Dunedin Income Growth Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0340609</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Ecofin Global Utilities &amp; Infrastructure Trust plc</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BD3V464</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Ecofin US Renewables Infrastructure Trust</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BMXZ812</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Edinburgh Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0305233</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Edinburgh Worldwide Investment Trust</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BHSRZC8</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>EJF Investments Ltd</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BF0D1M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>EPE Special Opportunities Limited</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BYW49X3</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>European Opportunities Trust plc</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0019772</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>F&amp;C Investment Trust</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BS88V64</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Fair Oaks Income Limited</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BSWVSD5</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Fidelity Asian Values plc</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0332231</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Fidelity China Special Situations PLC</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B62Z3C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Fidelity Emerging Markets Limited</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B4L0PD4</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Fidelity European Trust plc</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BK1PKQ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Fidelity Special Values plc</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BWXC7Y9</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Finsbury Growth &amp; Income Trust plc</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0781606</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Foresight Enterprise VCT</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B07YBS9</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Foresight Environmental Infrastructure Ltd</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BJL5FH8</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Foresight Solar Fund Ltd</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BD3QJR5</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Foresight Technology VCT plc</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BKF2JH0</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Foresight VCT plc</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B68K371</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Foresight Ventures VCT Plc</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BRBQ0C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Fuel Ventures VCT plc</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BP2RHT1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Gabelli Merchant Partners Plc</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BD8P074</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>GCP Asset Backed Income Fund Limited</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BPCSN74</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>GCP Infrastructure Investments Ltd</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B6173J1</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Geiger Counter Ltd</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B15FW33</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Global Opportunities Trust plc</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/3386257</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Golden Prospect Precious Metals Ltd</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B1G9T99</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Gore Street Energy Storage Fund plc</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BG0P0V7</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Greencoat Renewables plc</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BF4TVJ3</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Greencoat UK Wind plc</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B8SC6K5</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Gresham House Energy Storage Fund Plc</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BFX3K77</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Gresham House Income &amp; Growth 2 VCT Plc</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B01WL23</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Gresham House Income &amp; Growth VCT Plc</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B29BN19</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Gresham House Renewable Energy VCT 1 Plc</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B4L1399</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Gresham House Renewable Energy VCT 2 Plc</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B4KWC52</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Gresham House Renewable Energy VCT2 plc</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B43GVJ8</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Gresham House Renewable VCT 1 plc</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B4M2G81</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Ground Rents Income Fund plc</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B8K0LM4</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Guinness VCT plc</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BQD0HG3</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Hansa Investment Company Limited</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BKLFC18</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Hansa Investment Company Limited</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BKLFC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Harbourvest Global Private Equity</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BR30MJ8</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Hargreave Hale AIM VCT Plc</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B02WHS0</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Henderson Far East Income Ltd</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B1GXH75</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Henderson High Income Trust plc</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0958057</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Henderson Smaller Cos Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0906506</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Herald Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0422864</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>HG Capital Trust plc</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BJ0LT19</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>HICL Infrastructure plc</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BJLP1Y7</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Home REIT plc</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BJP5HK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ICG Enterprise Trust plc</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0329200</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ICG-Longbow Senior Secured UK Property Debt Invest</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B8C23S8</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Impax Environmental Markets plc</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/3123249</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>India Capital Growth Fund Ltd</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B0P8RJ6</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>International Biotechnology Trust plc</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0455934</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>International Public Partnerships Limited</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B188SR5</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Intuitive Investments Group plc</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BPTH6Y2</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Invesco Asia Dragon Trust Plc</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0453530</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Invesco Bond Income Plus Limited</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B6RMDP6</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Invesco Global Equity Income Trust plc</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B1DQ647</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Investment Co plc</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BV4FKD0</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>JPMorgan American Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BKZGVH6</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>JPMorgan Asia Growth and Income Plc</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0132077</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>JPMorgan China Growth &amp; Income Plc</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0343501</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>JPMorgan Claverhouse Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0342218</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>JPMorgan Emerging Europe, Middle East &amp; Africa Sec</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/3216473</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>JPMorgan Emerging Markets Dividend Income Plc</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B5ZZY91</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>JPMorgan Emerging Markets Growth &amp; Income Plc</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BMXWN18</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>JPMorgan European Discovery Trust plc</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BMTS0Z3</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>JPMorgan European Growth &amp; Income plc</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BPR9Y24</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>JPMorgan Global Core Assets Limited</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BWPKR30</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>JPMorgan Global Growth &amp; Income plc</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BYMKY69</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>JPMorgan India Growth &amp; Income plc</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0345035</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>JPMorgan Japanese Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0174002</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>JPMorgan UK Small Cap Growth &amp; Income plc</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BF7L8P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>JPMorgan US Smaller Companies Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BJL5F34</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>JZ Capital Partners Ltd</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BPNZ7G1</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Law Debenture Corporation plc</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/3142921</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Life Settlement Assets plc</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BF1Q4B0</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Lindsell Train Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BNKDVV7</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Literacy Capital plc</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BMF1L08</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Living REIT Plc</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BF0P7H5</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>LMS Capital plc</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B12MHD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Lowland Investment Company plc</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BNXGHS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>M&amp;G Credit Income Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BFYYL32</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Macau Property Opportunities Fund</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BGDYFV6</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Majedie Investments plc</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0555522</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Manchester &amp; London Inv Tst plc</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0225847</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Marwyn Value Investors Ltd</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BYTRG23</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Maven Income &amp; Growth VCT 4 plc</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B043QW8</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Maven Income &amp; Growth VCT 5 plc</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0205753</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Maven Income &amp; Growth VCT plc</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0412285</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Maven Income and Growth VCT 3 plc</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/3115376</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Maven Renovar VCT Plc</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B641BB8</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Mercantile Investment Trust Plc</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BF4JDH5</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Merchants Trust plc</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0580007</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Mid Wynd International Investment Trust Plc</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B6VTTK0</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Migo Opportunities Trust Plc</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/3436594</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Mobius Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BFZ7R98</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Molten Ventures plc</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BY7QYJ5</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Molten Ventures VCT plc</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0286714</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Monks Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/3051726</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Montanaro European Smaller Companies Trust plc</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BM8H3X0</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Montanaro Uk Smaller Cos Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BZ1H9L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Murray Income Trust plc</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0611112</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Murray International Trust plc</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BQZCCB7</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Neuberger Private Equity Partners</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B28ZZX8</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>New Star Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0263104</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>NextEnergy Solar Fund Ltd</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BJ0JVY0</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Nippon Active Value Fund plc</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BKLGLS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>North American Income Trust plc</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BJ00Z30</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>North Atlantic Smaller Cos Inv Tst plc</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BRDXZ87</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Northern 2 VCT plc</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0535643</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Northern 3 VCT plc</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/3115202</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Northern Venture Trust plc</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0645070</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Oakley Capital Investments Ltd</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B23DL39</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Oberon AIM VCT Plc</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B1SN386</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Octopus AIM VCT 2 plc</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B0JQZZ8</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Octopus AIM VCT plc</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/3420207</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Octopus Apollo VCT plc</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B17B347</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Octopus Future Generations VCT plc</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BNGFHX1</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Octopus Renewables Infrastructure Trust plc</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BJM0293</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Octopus Titan VCT plc</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B28V934</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Odyssean Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BFFK7H5</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Onward Opportunities Ltd</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BMZR151</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Oryx International Growth Fund</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B3BTVQ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Oxford Technology 2</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BN73FM9</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Oxford Technology 2</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BN73FP2</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Oxford Technology 2</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BN73FN0</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Oxford Technology 2 VCT plc</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0310505</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Pacific Assets Trust plc</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0667438</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Pacific Horizon Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0666747</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Pantheon Infrastructure Plc</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BLNNFL8</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Pantheon International Plc</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BP37WF1</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Partners Group Private Equity</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B28C2R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Partners Group Private Equity Ltd</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BF012D4</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Parvus Energy Efficiency Trust plc</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BN6JYS7</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Patria Private Equity Trust Plc</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/3047468</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Pembroke VCT plc</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BQVC9S7</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Pershing Square Holdings Ltd</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BS7JCJ8</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Personal Assets Trust plc</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BM8B5H0</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Phoenix Spree Deutschland Ltd</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BVG2VP8</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Polar Capital Global Financials Trust plc</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B9XQT11</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Polar Capital Global Healthcare Trust plc</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B6832P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Polar Capital Technology Trust plc</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BR3YV26</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Praetura Growth VCT plc</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BL690L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Proven Growth &amp; Income VCT plc</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B5B7YS0</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>ProVen VCT plc</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B8GH9P8</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Puma AIM VCT</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BRC8992</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Puma Alpha VCT plc</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BGMG7F1</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Puma VCT 13 Plc</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BD5B1L6</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Real Estate Credit Investments Ltd</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B0HW536</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Regional REIT Ltd</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BSY2LD7</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Residential Secure Income REIT</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BYSX150</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Rights &amp; Issues Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0739207</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>RIT Capital Partners plc</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0736639</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>River UK Micro Cap Red</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BNDMJP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Riverstone Credit Opportunities Income Plc</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BRBWLX3</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Riverstone Energy Ltd</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BWZ6KH3</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>RM Infrastructure Income plc</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BYMTBG5</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Rockwood Strategic Plc</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BRRD5L6</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>RTW Biotech Opportunities Ltd</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BKTRRM2</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Ruffer Investment Co Ltd</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B018CS4</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Schiehallion Fund Limited</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BJ0CDD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Schroder Asia Pacific Fund</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0791887</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Schroder Asian Total Return Investment Company plc</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0871079</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Schroder British Opportunities Trust</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BN7JZR2</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Schroder BSC Social Impact Trust plc</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BF78131</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Schroder European Real Estate Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BY7R8K7</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Schroder Income Growth Fund plc</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0791586</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Schroder Japan Trust plc</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0802284</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Schroder Oriental Income Fund</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B0CRWN5</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Schroder Real Estate Investment Trust Ltd</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B01HM14</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Schroder UK Mid Cap Fund plc</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0610841</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Schroders Capital Global Innovation Trust</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BVG1CF2</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Scottish American Investment Co plc</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0787369</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Scottish Mortgage Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BLDYK61</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Scottish Oriental Smaller Companies Trust plc</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BRBL657</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>SDCL Efficiency Income Trust Plc</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BGHVZM4</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Seed Innovations Limited</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BRK9BQ8</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Seneca Growth Capital VCT plc</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BG13MH0</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Seneca Growth Capital VCT Plc</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/3125610</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Sequoia Economic Infrastructure Income Fund Ltd</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BV54HY6</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Seraphim Space Investment Trust</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BW6HS59</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Seraphim Space Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BKPG013</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Sherborne Investors C</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BZ3C3B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Strategic Equity Capital plc</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B0BDCB2</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>STS Global Income &amp; Growth Trust plc</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B09G3N2</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Symphony International Holdings Ltd</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B231M63</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Syncona Limited</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B8P59C0</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Target Healthcare REIT plc</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BJGTLF5</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Temple Bar Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BMV92D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Templeton Emerging Markets Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BKPG0S0</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Tetragon Financial Group Ltd</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BFNSMW1</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Tetragon Financial Group Ltd</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B28ZZS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>The European Smaller Companies Trust plc</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BMCF868</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>The Global Smaller Companies Trust Plc</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BKLXD97</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>The Renewables Infrastructure Group Limited</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BBHX2H9</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>TR Property Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0906409</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Triple Point VCT 2011 Plc</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BDTYGZ0</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Tritax Big Box REIT plc</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BG49KP9</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Tufton Assets Limited</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BSFVPB9</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>TwentyFour Income Fund Ltd</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B90J5Z9</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>TwentyFour Select Monthly Income Fund Limited</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BJVDZ94</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Unicorn AIM VCT plc</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B1RTFN4</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>US Solar Fund Plc</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BHZ6410</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Utilico Emerging Markets Trust plc</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BD45S96</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Value and Indexed Property Income Trust</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/0848471</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>VH Global Energy Infrastructure Plc</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BNKVP75</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Vietnam Enterprise Investments Ltd</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BD9X204</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>VinaCapital Vietnam Opportunity Fund Ltd</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BYXVT88</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Volta Finance Ltd</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/B28Y104</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Volta Finance Ltd</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BFZ4H11</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>VPC Specialty Lending Investments plc</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BVG6X43</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Worldwide Healthcare Trust plc</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BN455J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Worsley Investors Limited</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hl.co.uk/shares/shares-search-results/BHXH0C8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C307" r:id="rId306"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
